--- a/reference/us_reconductoring_projects.xlsx
+++ b/reference/us_reconductoring_projects.xlsx
@@ -25,13 +25,19 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -42,7 +48,14 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -52,15 +65,27 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -2835,11 +2860,11 @@
     <col width="12.43357142857143" bestFit="1" customWidth="1" style="2" min="4" max="4"/>
     <col width="12.43357142857143" bestFit="1" customWidth="1" style="2" min="5" max="5"/>
     <col width="12.43357142857143" bestFit="1" customWidth="1" style="2" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="110" customWidth="1" min="11" max="11"/>
+    <col width="24.005" bestFit="1" customWidth="1" style="2" min="7" max="7"/>
+    <col width="14.005" bestFit="1" customWidth="1" style="2" min="8" max="8"/>
+    <col width="14.005" bestFit="1" customWidth="1" style="2" min="9" max="9"/>
+    <col width="14.005" bestFit="1" customWidth="1" style="2" min="10" max="10"/>
+    <col width="110.005" bestFit="1" customWidth="1" style="6" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.25" customHeight="1">
@@ -2893,59 +2918,60 @@
           <t>Planned Year</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="17.25" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="17.25" customFormat="1" customHeight="1" s="4">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Cayuga - Wolf Creek 345 kV baseline transmission upgrade</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>CAYUGA</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>WOLF CREEK</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>Baseline reliability upgrade</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>345</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>MISO</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>Duke Energy Indiana</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="H2" s="6" t="n"/>
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>2029</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>Coordinated MISO baseline transmission upgrades rebuild and reconductor the 345 kV lines connecting Cayuga, Nucor, and Wolf Creek. The program includes a $96 million Cayuga-to-Nucor rebuild and a $49 million Nucor-to-Wolf Creek rebuild targeted for completion by June 2029.</t>
         </is>
@@ -2982,6 +3008,11 @@
           <t>MISO</t>
         </is>
       </c>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="6" t="n"/>
     </row>
     <row r="4" ht="17.25" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -3014,6 +3045,11 @@
           <t>MISO</t>
         </is>
       </c>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="6" t="n"/>
     </row>
     <row r="5" ht="17.25" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -3046,6 +3082,11 @@
           <t>MISO</t>
         </is>
       </c>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="6" t="n"/>
     </row>
     <row r="6" ht="17.25" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -3078,6 +3119,11 @@
           <t>MISO</t>
         </is>
       </c>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="6" t="n"/>
     </row>
     <row r="7" ht="17.25" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -3110,6 +3156,11 @@
           <t>MISO</t>
         </is>
       </c>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="6" t="n"/>
     </row>
     <row r="8" ht="17.25" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -3142,6 +3193,11 @@
           <t>MISO</t>
         </is>
       </c>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3336,20 +3392,21 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12.43357142857143" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
+    <col width="72" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
     <col width="20.57642857142857" bestFit="1" customWidth="1" style="2" min="2" max="2"/>
     <col width="12.43357142857143" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
-    <col width="12.43357142857143" bestFit="1" customWidth="1" style="2" min="4" max="4"/>
+    <col width="52" bestFit="1" customWidth="1" style="2" min="4" max="4"/>
     <col width="12.43357142857143" bestFit="1" customWidth="1" style="2" min="5" max="5"/>
     <col width="12.43357142857143" bestFit="1" customWidth="1" style="2" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="110" customWidth="1" min="11" max="11"/>
+    <col width="24" bestFit="1" customWidth="1" style="2" min="7" max="7"/>
+    <col width="16" bestFit="1" customWidth="1" style="2" min="8" max="8"/>
+    <col width="14" bestFit="1" customWidth="1" style="2" min="9" max="9"/>
+    <col width="14.005" bestFit="1" customWidth="1" style="2" min="10" max="10"/>
+    <col width="110" bestFit="1" customWidth="1" style="6" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.25" customHeight="1">
@@ -3403,9 +3460,14 @@
           <t>Planned Year</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>Description</t>
+        </is>
+      </c>
+      <c r="L1" s="6" t="inlineStr">
+        <is>
+          <t>Rating</t>
         </is>
       </c>
     </row>
@@ -3440,6 +3502,11 @@
           <t>PJM</t>
         </is>
       </c>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="6" t="n"/>
     </row>
     <row r="3" ht="17.25" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -3472,6 +3539,11 @@
           <t>PJM</t>
         </is>
       </c>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="6" t="n"/>
     </row>
     <row r="4" ht="17.25" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -3504,6 +3576,11 @@
           <t>PJM</t>
         </is>
       </c>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="6" t="n"/>
     </row>
     <row r="5" ht="17.25" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -3536,6 +3613,11 @@
           <t>PJM</t>
         </is>
       </c>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="6" t="n"/>
     </row>
     <row r="6" ht="17.25" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -3568,6 +3650,11 @@
           <t>PJM</t>
         </is>
       </c>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="6" t="n"/>
     </row>
     <row r="7" ht="17.25" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -3600,6 +3687,11 @@
           <t>PJM</t>
         </is>
       </c>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="6" t="n"/>
     </row>
     <row r="8" ht="17.25" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -3632,6 +3724,11 @@
           <t>PJM</t>
         </is>
       </c>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="6" t="n"/>
     </row>
     <row r="9" ht="17.25" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -3664,8 +3761,13 @@
           <t>PJM</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="17.25" customHeight="1">
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="n"/>
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="28.5" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>LICK - JEFFERSON 69 kV reconductoring project</t>
@@ -3696,7 +3798,11 @@
           <t>PJM</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="n"/>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="6" t="inlineStr">
         <is>
           <t>Reconductoring project for the existing LICK - JEFFERSON 69 kV transmission line in the PJM region. Utility, distance, rating, cost, status, and planned-year details are not available in the current project source data.</t>
         </is>
@@ -3733,54 +3839,60 @@
           <t>PJM</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="17.25" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="6" t="n"/>
+    </row>
+    <row r="12" ht="84.75" customFormat="1" customHeight="1" s="4">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Chesterfield - Tyler 230 kV transmission rebuild and reconductor project</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>CHESTERFIELD</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>TYLER</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>Supplemental transmission planning reliability upgrade</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>PJM</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>Dominion Energy</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>2.9</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>Planned</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="J12" s="6" t="n"/>
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>Rebuild and reconductor 2.9 miles of overhead transmission line from the Chesterfield Substation to just south of the Tyler Substation in Chesterfield County, Virginia. The operating voltage will remain 230 kV while new structures and higher-capacity conductors replace aging infrastructure, increase ampacity, and support regional data center growth, local generation, and reliability needs through Dominion Energy's supplemental transmission planning process.</t>
         </is>
@@ -3817,6 +3929,11 @@
           <t>PJM</t>
         </is>
       </c>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="n"/>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="6" t="n"/>
     </row>
     <row r="14" ht="17.25" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -3849,6 +3966,11 @@
           <t>PJM</t>
         </is>
       </c>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="6" t="n"/>
     </row>
     <row r="15" ht="17.25" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
@@ -3881,6 +4003,11 @@
           <t>PJM</t>
         </is>
       </c>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="n"/>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="6" t="n"/>
     </row>
     <row r="16" ht="17.25" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -3913,6 +4040,11 @@
           <t>PJM</t>
         </is>
       </c>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="6" t="n"/>
     </row>
     <row r="17" ht="17.25" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
@@ -3945,6 +4077,11 @@
           <t>PJM</t>
         </is>
       </c>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="6" t="n"/>
     </row>
     <row r="18" ht="17.25" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -3977,6 +4114,11 @@
           <t>PJM</t>
         </is>
       </c>
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="6" t="n"/>
     </row>
     <row r="19" ht="17.25" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
@@ -4009,6 +4151,11 @@
           <t>PJM</t>
         </is>
       </c>
+      <c r="G19" s="2" t="n"/>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="6" t="n"/>
     </row>
     <row r="20" ht="17.25" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -4041,6 +4188,11 @@
           <t>PJM</t>
         </is>
       </c>
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="n"/>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="6" t="n"/>
     </row>
     <row r="21" ht="17.25" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
@@ -4073,6 +4225,11 @@
           <t>PJM</t>
         </is>
       </c>
+      <c r="G21" s="2" t="n"/>
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="n"/>
+      <c r="J21" s="2" t="n"/>
+      <c r="K21" s="6" t="n"/>
     </row>
     <row r="22" ht="17.25" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -4105,6 +4262,11 @@
           <t>PJM</t>
         </is>
       </c>
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="6" t="n"/>
     </row>
     <row r="23" ht="17.25" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
@@ -4137,6 +4299,11 @@
           <t>PJM</t>
         </is>
       </c>
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="n"/>
+      <c r="J23" s="2" t="n"/>
+      <c r="K23" s="6" t="n"/>
     </row>
     <row r="24" ht="17.25" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -4167,6 +4334,494 @@
       <c r="F24" s="2" t="inlineStr">
         <is>
           <t>PJM</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="n"/>
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="n"/>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="6" t="n"/>
+    </row>
+    <row r="25" ht="90" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Leroy Center - Mayfield Q1 138 kV reconductoring need</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>LEROY CENTER</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>MAYFIELD</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Existing reconductoring</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>PJM</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>ATSI</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>16.1</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
+        <is>
+          <t>The Leroy Center - Mayfield Q1 138 kV line is approximately 16.1 miles long and was originally constructed in the mid-1940s. The Leroy Center - Pawnee Tap Q1 138 kV section, approximately 8.4 miles, is being reconductored under RTEP project B3152. The remaining Pawnee Tap - Mayfield Q1 138 kV section is approximately 7.7 miles, with aging structures, conductors, and hardware.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="90" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Powell County - Zachariah 69 kV reconductoring-related structural reliability upgrade</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>POWELL COUNTY</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>ZACHARIAH</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Reconductoring-related structural reliability upgrade</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>PJM</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>EKPC</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>16.85</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="K26" s="7" t="inlineStr">
+        <is>
+          <t>The 16.85-mile Powell County - Zachariah 69 kV line was built in 1954. EKPC identified the line for structural loading concerns associated with single wood-pole structures and 556.5 ACSR wire or larger. The source notes that many lines in the program have previously been reconductored with larger wire without corresponding structural design work; alternatives will be developed to address the remaining structural concerns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="90" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Rob Park - Lincoln 138 kV line rebuild and reconductoring</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>ROB PARK</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>LINCOLN</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Existing line rebuild and reconductoring</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>PJM</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>AEP</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>10.9 / 7.8</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>The Robison Park - Lincoln 138 kV line is approximately 10.9/7.8 miles long and has 44 structures with open conditions, including rusted legs, damaged insulators, and rusted shield wire. The line does not meet current AEP structural-strength or shield-angle requirements. The upper tower sections were replaced and reconductored in 1968 for 138 kV operation, while the lower sections and foundations date to the original 1928 installation. The remaining 3.1 miles are covered under AEP-2019-IM038 and will be addressed through a future solution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="90" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Remington CT - Elk Run 230 kV Line 2114 reconductoring</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>REMINGTON CT</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>ELK RUN</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Approved baseline reconductoring</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>PJM</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Dominion Energy</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>3.46</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>Under approved baseline solution b3689.1, reconductor approximately 3.46 miles of 230 kV Line 2114 from Remington CT to Elk Run using higher-capacity conductor to achieve an expected 1573 MVA rating.</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>1573 MVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="90" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Elk Run - Rollins Ford 230 kV Line 2114 reconductoring</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>ELK RUN</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>ROLLINS FORD</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Approved baseline reconductoring</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>PJM</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Dominion Energy</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>19.71</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>Under approved baseline solution b3689.1, reconductor approximately 19.71 miles of 230 kV Line 2114 from Elk Run to Rollins Ford using higher-capacity conductor to achieve an expected 1573 MVA rating.</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>1573 MVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="90" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Rollins Ford - Gainesville 230 kV Line 2222 reconductoring</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>ROLLINS FORD</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>GAINESVILLE</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Approved baseline reconductoring</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>PJM</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Dominion Energy</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="K30" s="7" t="inlineStr">
+        <is>
+          <t>Under approved baseline solution b3689.1, reconductor approximately 1.11 miles of 230 kV Line 2222 from Rollins Ford to Gainesville using higher-capacity conductor to achieve an expected 1573 MVA rating.</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>1573 MVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="90" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Elizabethtown - Central Hardin - Stephensburg 69 kV reconductoring-related structural reliability upgrade</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>ELIZABETHTOWN</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>STEPHENSBURG</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Reconductoring-related structural reliability upgrade</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>PJM</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>EKPC</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>11.7</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>EKPC identified the 11.7-mile Elizabethtown - Central Hardin - Stephensburg 69 kV line sections for structural loading concerns. The source notes that many lines in the program have been reconductored with larger wire while receiving limited structural design work; alternatives will be developed to address the structural concerns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="90" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Elizabethtown - Patriot Parkway - Vine Grove 69 kV reconductoring-related structural reliability upgrade</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>ELIZABETHTOWN</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>VINE GROVE</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Reconductoring-related structural reliability upgrade</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>PJM</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>EKPC</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>7.45</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="K32" s="7" t="inlineStr">
+        <is>
+          <t>EKPC identified the 7.45-mile Elizabethtown - Patriot Parkway - Vine Grove 69 kV line sections for structural loading concerns. The source notes that many lines in the program have been reconductored with larger wire while receiving limited structural design work; alternatives will be developed to address the structural concerns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="90" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Windsor - Somerset 69 kV reconductoring-related structural reliability upgrade</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>WINDSOR</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>SOMERSET</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Reconductoring-related structural reliability upgrade</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>PJM</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>EKPC</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>18.97</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="K33" s="7" t="inlineStr">
+        <is>
+          <t>EKPC identified the 18.97-mile Windsor - Somerset 69 kV line sections for structural loading concerns. The source notes that many lines in the program have been reconductored with larger wire while receiving limited structural design work; alternatives will be developed to address the structural concerns.</t>
         </is>
       </c>
     </row>

--- a/reference/us_reconductoring_projects.xlsx
+++ b/reference/us_reconductoring_projects.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC146"/>
+  <dimension ref="A1:BF147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -699,6 +699,21 @@
       <c r="BC1" t="inlineStr">
         <is>
           <t>Source - Transmission Plan Approved</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>Conductor Type</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>EPRI Case URL</t>
         </is>
       </c>
     </row>
@@ -772,7 +787,7 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
-      <c r="X2" t="b">
+      <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="inlineStr"/>
@@ -806,6 +821,9 @@
       <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -877,7 +895,7 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
-      <c r="X3" t="b">
+      <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="inlineStr"/>
@@ -911,6 +929,9 @@
       <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -982,7 +1003,7 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
-      <c r="X4" t="b">
+      <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="inlineStr"/>
@@ -1016,6 +1037,9 @@
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1087,7 +1111,7 @@
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
-      <c r="X5" t="b">
+      <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="inlineStr"/>
@@ -1121,6 +1145,9 @@
       <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1192,7 +1219,7 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
-      <c r="X6" t="b">
+      <c r="X6" t="n">
         <v>0</v>
       </c>
       <c r="Y6" t="inlineStr"/>
@@ -1226,6 +1253,9 @@
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="inlineStr"/>
       <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1297,7 +1327,7 @@
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
-      <c r="X7" t="b">
+      <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="inlineStr"/>
@@ -1331,6 +1361,9 @@
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="inlineStr"/>
       <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1402,7 +1435,7 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
-      <c r="X8" t="b">
+      <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="inlineStr"/>
@@ -1436,6 +1469,9 @@
       <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="inlineStr"/>
       <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1507,7 +1543,7 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
-      <c r="X9" t="b">
+      <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="inlineStr"/>
@@ -1541,6 +1577,9 @@
       <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="inlineStr"/>
       <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1612,7 +1651,7 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
-      <c r="X10" t="b">
+      <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="inlineStr"/>
@@ -1646,6 +1685,9 @@
       <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="inlineStr"/>
       <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1718,7 +1760,7 @@
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
-      <c r="X11" t="b">
+      <c r="X11" t="n">
         <v>1</v>
       </c>
       <c r="Y11" t="inlineStr"/>
@@ -1752,6 +1794,9 @@
       <c r="BA11" t="inlineStr"/>
       <c r="BB11" t="inlineStr"/>
       <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1823,7 +1868,7 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
-      <c r="X12" t="b">
+      <c r="X12" t="n">
         <v>0</v>
       </c>
       <c r="Y12" t="inlineStr"/>
@@ -1857,6 +1902,9 @@
       <c r="BA12" t="inlineStr"/>
       <c r="BB12" t="inlineStr"/>
       <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1928,7 +1976,7 @@
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
-      <c r="X13" t="b">
+      <c r="X13" t="n">
         <v>1</v>
       </c>
       <c r="Y13" t="inlineStr"/>
@@ -1962,6 +2010,9 @@
       <c r="BA13" t="inlineStr"/>
       <c r="BB13" t="inlineStr"/>
       <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2033,7 +2084,7 @@
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
-      <c r="X14" t="b">
+      <c r="X14" t="n">
         <v>0</v>
       </c>
       <c r="Y14" t="inlineStr"/>
@@ -2067,6 +2118,9 @@
       <c r="BA14" t="inlineStr"/>
       <c r="BB14" t="inlineStr"/>
       <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2138,7 +2192,7 @@
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
-      <c r="X15" t="b">
+      <c r="X15" t="n">
         <v>0</v>
       </c>
       <c r="Y15" t="inlineStr"/>
@@ -2172,6 +2226,9 @@
       <c r="BA15" t="inlineStr"/>
       <c r="BB15" t="inlineStr"/>
       <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2243,7 +2300,7 @@
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
-      <c r="X16" t="b">
+      <c r="X16" t="n">
         <v>0</v>
       </c>
       <c r="Y16" t="inlineStr"/>
@@ -2277,6 +2334,9 @@
       <c r="BA16" t="inlineStr"/>
       <c r="BB16" t="inlineStr"/>
       <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2348,7 +2408,7 @@
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
-      <c r="X17" t="b">
+      <c r="X17" t="n">
         <v>0</v>
       </c>
       <c r="Y17" t="inlineStr"/>
@@ -2382,6 +2442,9 @@
       <c r="BA17" t="inlineStr"/>
       <c r="BB17" t="inlineStr"/>
       <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2453,7 +2516,7 @@
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
-      <c r="X18" t="b">
+      <c r="X18" t="n">
         <v>1</v>
       </c>
       <c r="Y18" t="inlineStr"/>
@@ -2487,6 +2550,9 @@
       <c r="BA18" t="inlineStr"/>
       <c r="BB18" t="inlineStr"/>
       <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr"/>
+      <c r="BF18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2558,7 +2624,7 @@
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
-      <c r="X19" t="b">
+      <c r="X19" t="n">
         <v>0</v>
       </c>
       <c r="Y19" t="inlineStr"/>
@@ -2592,6 +2658,9 @@
       <c r="BA19" t="inlineStr"/>
       <c r="BB19" t="inlineStr"/>
       <c r="BC19" t="inlineStr"/>
+      <c r="BD19" t="inlineStr"/>
+      <c r="BE19" t="inlineStr"/>
+      <c r="BF19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2663,7 +2732,7 @@
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
-      <c r="X20" t="b">
+      <c r="X20" t="n">
         <v>1</v>
       </c>
       <c r="Y20" t="inlineStr"/>
@@ -2697,6 +2766,9 @@
       <c r="BA20" t="inlineStr"/>
       <c r="BB20" t="inlineStr"/>
       <c r="BC20" t="inlineStr"/>
+      <c r="BD20" t="inlineStr"/>
+      <c r="BE20" t="inlineStr"/>
+      <c r="BF20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2768,7 +2840,7 @@
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
-      <c r="X21" t="b">
+      <c r="X21" t="n">
         <v>1</v>
       </c>
       <c r="Y21" t="inlineStr"/>
@@ -2802,6 +2874,9 @@
       <c r="BA21" t="inlineStr"/>
       <c r="BB21" t="inlineStr"/>
       <c r="BC21" t="inlineStr"/>
+      <c r="BD21" t="inlineStr"/>
+      <c r="BE21" t="inlineStr"/>
+      <c r="BF21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2873,7 +2948,7 @@
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
-      <c r="X22" t="b">
+      <c r="X22" t="n">
         <v>1</v>
       </c>
       <c r="Y22" t="inlineStr"/>
@@ -2907,6 +2982,9 @@
       <c r="BA22" t="inlineStr"/>
       <c r="BB22" t="inlineStr"/>
       <c r="BC22" t="inlineStr"/>
+      <c r="BD22" t="inlineStr"/>
+      <c r="BE22" t="inlineStr"/>
+      <c r="BF22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2978,7 +3056,7 @@
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
-      <c r="X23" t="b">
+      <c r="X23" t="n">
         <v>0</v>
       </c>
       <c r="Y23" t="inlineStr"/>
@@ -3012,6 +3090,9 @@
       <c r="BA23" t="inlineStr"/>
       <c r="BB23" t="inlineStr"/>
       <c r="BC23" t="inlineStr"/>
+      <c r="BD23" t="inlineStr"/>
+      <c r="BE23" t="inlineStr"/>
+      <c r="BF23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3083,7 +3164,7 @@
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
-      <c r="X24" t="b">
+      <c r="X24" t="n">
         <v>0</v>
       </c>
       <c r="Y24" t="inlineStr"/>
@@ -3117,6 +3198,9 @@
       <c r="BA24" t="inlineStr"/>
       <c r="BB24" t="inlineStr"/>
       <c r="BC24" t="inlineStr"/>
+      <c r="BD24" t="inlineStr"/>
+      <c r="BE24" t="inlineStr"/>
+      <c r="BF24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3188,7 +3272,7 @@
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
-      <c r="X25" t="b">
+      <c r="X25" t="n">
         <v>0</v>
       </c>
       <c r="Y25" t="inlineStr"/>
@@ -3222,6 +3306,9 @@
       <c r="BA25" t="inlineStr"/>
       <c r="BB25" t="inlineStr"/>
       <c r="BC25" t="inlineStr"/>
+      <c r="BD25" t="inlineStr"/>
+      <c r="BE25" t="inlineStr"/>
+      <c r="BF25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3293,7 +3380,7 @@
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
-      <c r="X26" t="b">
+      <c r="X26" t="n">
         <v>1</v>
       </c>
       <c r="Y26" t="inlineStr"/>
@@ -3327,6 +3414,9 @@
       <c r="BA26" t="inlineStr"/>
       <c r="BB26" t="inlineStr"/>
       <c r="BC26" t="inlineStr"/>
+      <c r="BD26" t="inlineStr"/>
+      <c r="BE26" t="inlineStr"/>
+      <c r="BF26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3398,7 +3488,7 @@
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr"/>
-      <c r="X27" t="b">
+      <c r="X27" t="n">
         <v>1</v>
       </c>
       <c r="Y27" t="inlineStr"/>
@@ -3432,6 +3522,9 @@
       <c r="BA27" t="inlineStr"/>
       <c r="BB27" t="inlineStr"/>
       <c r="BC27" t="inlineStr"/>
+      <c r="BD27" t="inlineStr"/>
+      <c r="BE27" t="inlineStr"/>
+      <c r="BF27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3503,7 +3596,7 @@
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
-      <c r="X28" t="b">
+      <c r="X28" t="n">
         <v>0</v>
       </c>
       <c r="Y28" t="inlineStr"/>
@@ -3537,6 +3630,9 @@
       <c r="BA28" t="inlineStr"/>
       <c r="BB28" t="inlineStr"/>
       <c r="BC28" t="inlineStr"/>
+      <c r="BD28" t="inlineStr"/>
+      <c r="BE28" t="inlineStr"/>
+      <c r="BF28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3608,7 +3704,7 @@
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
-      <c r="X29" t="b">
+      <c r="X29" t="n">
         <v>0</v>
       </c>
       <c r="Y29" t="inlineStr"/>
@@ -3642,6 +3738,9 @@
       <c r="BA29" t="inlineStr"/>
       <c r="BB29" t="inlineStr"/>
       <c r="BC29" t="inlineStr"/>
+      <c r="BD29" t="inlineStr"/>
+      <c r="BE29" t="inlineStr"/>
+      <c r="BF29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3713,7 +3812,7 @@
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
-      <c r="X30" t="b">
+      <c r="X30" t="n">
         <v>0</v>
       </c>
       <c r="Y30" t="inlineStr"/>
@@ -3747,6 +3846,9 @@
       <c r="BA30" t="inlineStr"/>
       <c r="BB30" t="inlineStr"/>
       <c r="BC30" t="inlineStr"/>
+      <c r="BD30" t="inlineStr"/>
+      <c r="BE30" t="inlineStr"/>
+      <c r="BF30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3818,7 +3920,7 @@
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
-      <c r="X31" t="b">
+      <c r="X31" t="n">
         <v>0</v>
       </c>
       <c r="Y31" t="inlineStr"/>
@@ -3852,6 +3954,9 @@
       <c r="BA31" t="inlineStr"/>
       <c r="BB31" t="inlineStr"/>
       <c r="BC31" t="inlineStr"/>
+      <c r="BD31" t="inlineStr"/>
+      <c r="BE31" t="inlineStr"/>
+      <c r="BF31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3923,7 +4028,7 @@
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr"/>
-      <c r="X32" t="b">
+      <c r="X32" t="n">
         <v>1</v>
       </c>
       <c r="Y32" t="inlineStr"/>
@@ -3957,6 +4062,9 @@
       <c r="BA32" t="inlineStr"/>
       <c r="BB32" t="inlineStr"/>
       <c r="BC32" t="inlineStr"/>
+      <c r="BD32" t="inlineStr"/>
+      <c r="BE32" t="inlineStr"/>
+      <c r="BF32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4028,7 +4136,7 @@
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
-      <c r="X33" t="b">
+      <c r="X33" t="n">
         <v>0</v>
       </c>
       <c r="Y33" t="inlineStr"/>
@@ -4062,6 +4170,9 @@
       <c r="BA33" t="inlineStr"/>
       <c r="BB33" t="inlineStr"/>
       <c r="BC33" t="inlineStr"/>
+      <c r="BD33" t="inlineStr"/>
+      <c r="BE33" t="inlineStr"/>
+      <c r="BF33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4133,7 +4244,7 @@
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr"/>
-      <c r="X34" t="b">
+      <c r="X34" t="n">
         <v>0</v>
       </c>
       <c r="Y34" t="inlineStr"/>
@@ -4167,6 +4278,9 @@
       <c r="BA34" t="inlineStr"/>
       <c r="BB34" t="inlineStr"/>
       <c r="BC34" t="inlineStr"/>
+      <c r="BD34" t="inlineStr"/>
+      <c r="BE34" t="inlineStr"/>
+      <c r="BF34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4266,7 +4380,7 @@
           <t>2026-04-27T00:00:00</t>
         </is>
       </c>
-      <c r="X35" t="b">
+      <c r="X35" t="n">
         <v>0</v>
       </c>
       <c r="Y35" t="inlineStr"/>
@@ -4300,6 +4414,9 @@
       <c r="BA35" t="inlineStr"/>
       <c r="BB35" t="inlineStr"/>
       <c r="BC35" t="inlineStr"/>
+      <c r="BD35" t="inlineStr"/>
+      <c r="BE35" t="inlineStr"/>
+      <c r="BF35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4395,7 +4512,7 @@
           <t>2027-12-23T00:00:00</t>
         </is>
       </c>
-      <c r="X36" t="b">
+      <c r="X36" t="n">
         <v>0</v>
       </c>
       <c r="Y36" t="inlineStr"/>
@@ -4429,6 +4546,9 @@
       <c r="BA36" t="inlineStr"/>
       <c r="BB36" t="inlineStr"/>
       <c r="BC36" t="inlineStr"/>
+      <c r="BD36" t="inlineStr"/>
+      <c r="BE36" t="inlineStr"/>
+      <c r="BF36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4528,7 +4648,7 @@
           <t>2026-08-26T00:00:00</t>
         </is>
       </c>
-      <c r="X37" t="b">
+      <c r="X37" t="n">
         <v>0</v>
       </c>
       <c r="Y37" t="inlineStr"/>
@@ -4562,6 +4682,9 @@
       <c r="BA37" t="inlineStr"/>
       <c r="BB37" t="inlineStr"/>
       <c r="BC37" t="inlineStr"/>
+      <c r="BD37" t="inlineStr"/>
+      <c r="BE37" t="inlineStr"/>
+      <c r="BF37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4655,7 +4778,7 @@
           <t>2025-10-01T00:00:00</t>
         </is>
       </c>
-      <c r="X38" t="b">
+      <c r="X38" t="n">
         <v>1</v>
       </c>
       <c r="Y38" t="inlineStr"/>
@@ -4689,6 +4812,9 @@
       <c r="BA38" t="inlineStr"/>
       <c r="BB38" t="inlineStr"/>
       <c r="BC38" t="inlineStr"/>
+      <c r="BD38" t="inlineStr"/>
+      <c r="BE38" t="inlineStr"/>
+      <c r="BF38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4776,7 +4902,7 @@
           <t>Pending</t>
         </is>
       </c>
-      <c r="X39" t="b">
+      <c r="X39" t="n">
         <v>0</v>
       </c>
       <c r="Y39" t="inlineStr"/>
@@ -4810,6 +4936,9 @@
       <c r="BA39" t="inlineStr"/>
       <c r="BB39" t="inlineStr"/>
       <c r="BC39" t="inlineStr"/>
+      <c r="BD39" t="inlineStr"/>
+      <c r="BE39" t="inlineStr"/>
+      <c r="BF39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4909,7 +5038,7 @@
           <t>2024-01-15T00:00:00</t>
         </is>
       </c>
-      <c r="X40" t="b">
+      <c r="X40" t="n">
         <v>1</v>
       </c>
       <c r="Y40" t="inlineStr"/>
@@ -4943,6 +5072,9 @@
       <c r="BA40" t="inlineStr"/>
       <c r="BB40" t="inlineStr"/>
       <c r="BC40" t="inlineStr"/>
+      <c r="BD40" t="inlineStr"/>
+      <c r="BE40" t="inlineStr"/>
+      <c r="BF40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5020,7 +5152,7 @@
           <t>2021-05-17T00:00:00</t>
         </is>
       </c>
-      <c r="X41" t="b">
+      <c r="X41" t="n">
         <v>1</v>
       </c>
       <c r="Y41" t="inlineStr"/>
@@ -5054,6 +5186,9 @@
       <c r="BA41" t="inlineStr"/>
       <c r="BB41" t="inlineStr"/>
       <c r="BC41" t="inlineStr"/>
+      <c r="BD41" t="inlineStr"/>
+      <c r="BE41" t="inlineStr"/>
+      <c r="BF41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5137,7 +5272,7 @@
           <t>2022-02-04T00:00:00</t>
         </is>
       </c>
-      <c r="X42" t="b">
+      <c r="X42" t="n">
         <v>0</v>
       </c>
       <c r="Y42" t="inlineStr"/>
@@ -5171,6 +5306,9 @@
       <c r="BA42" t="inlineStr"/>
       <c r="BB42" t="inlineStr"/>
       <c r="BC42" t="inlineStr"/>
+      <c r="BD42" t="inlineStr"/>
+      <c r="BE42" t="inlineStr"/>
+      <c r="BF42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5266,7 +5404,7 @@
           <t>2024-06-24T00:00:00</t>
         </is>
       </c>
-      <c r="X43" t="b">
+      <c r="X43" t="n">
         <v>0</v>
       </c>
       <c r="Y43" t="inlineStr"/>
@@ -5300,6 +5438,9 @@
       <c r="BA43" t="inlineStr"/>
       <c r="BB43" t="inlineStr"/>
       <c r="BC43" t="inlineStr"/>
+      <c r="BD43" t="inlineStr"/>
+      <c r="BE43" t="inlineStr"/>
+      <c r="BF43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5381,7 +5522,7 @@
           <t>TBD</t>
         </is>
       </c>
-      <c r="X44" t="b">
+      <c r="X44" t="n">
         <v>0</v>
       </c>
       <c r="Y44" t="inlineStr"/>
@@ -5415,6 +5556,9 @@
       <c r="BA44" t="inlineStr"/>
       <c r="BB44" t="inlineStr"/>
       <c r="BC44" t="inlineStr"/>
+      <c r="BD44" t="inlineStr"/>
+      <c r="BE44" t="inlineStr"/>
+      <c r="BF44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5510,7 +5654,7 @@
           <t>2027-02-02T00:00:00</t>
         </is>
       </c>
-      <c r="X45" t="b">
+      <c r="X45" t="n">
         <v>0</v>
       </c>
       <c r="Y45" t="inlineStr"/>
@@ -5544,6 +5688,9 @@
       <c r="BA45" t="inlineStr"/>
       <c r="BB45" t="inlineStr"/>
       <c r="BC45" t="inlineStr"/>
+      <c r="BD45" t="inlineStr"/>
+      <c r="BE45" t="inlineStr"/>
+      <c r="BF45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5643,7 +5790,7 @@
           <t>2028-06-05T00:00:00</t>
         </is>
       </c>
-      <c r="X46" t="b">
+      <c r="X46" t="n">
         <v>0</v>
       </c>
       <c r="Y46" t="inlineStr"/>
@@ -5677,6 +5824,9 @@
       <c r="BA46" t="inlineStr"/>
       <c r="BB46" t="inlineStr"/>
       <c r="BC46" t="inlineStr"/>
+      <c r="BD46" t="inlineStr"/>
+      <c r="BE46" t="inlineStr"/>
+      <c r="BF46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5776,7 +5926,7 @@
           <t>2027-01-06T00:00:00</t>
         </is>
       </c>
-      <c r="X47" t="b">
+      <c r="X47" t="n">
         <v>0</v>
       </c>
       <c r="Y47" t="inlineStr"/>
@@ -5810,6 +5960,9 @@
       <c r="BA47" t="inlineStr"/>
       <c r="BB47" t="inlineStr"/>
       <c r="BC47" t="inlineStr"/>
+      <c r="BD47" t="inlineStr"/>
+      <c r="BE47" t="inlineStr"/>
+      <c r="BF47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5909,7 +6062,7 @@
           <t>2023-11-01T00:00:00</t>
         </is>
       </c>
-      <c r="X48" t="b">
+      <c r="X48" t="n">
         <v>0</v>
       </c>
       <c r="Y48" t="inlineStr"/>
@@ -5943,6 +6096,9 @@
       <c r="BA48" t="inlineStr"/>
       <c r="BB48" t="inlineStr"/>
       <c r="BC48" t="inlineStr"/>
+      <c r="BD48" t="inlineStr"/>
+      <c r="BE48" t="inlineStr"/>
+      <c r="BF48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6038,7 +6194,7 @@
           <t>2023-09-21T00:00:00</t>
         </is>
       </c>
-      <c r="X49" t="b">
+      <c r="X49" t="n">
         <v>0</v>
       </c>
       <c r="Y49" t="inlineStr"/>
@@ -6072,6 +6228,9 @@
       <c r="BA49" t="inlineStr"/>
       <c r="BB49" t="inlineStr"/>
       <c r="BC49" t="inlineStr"/>
+      <c r="BD49" t="inlineStr"/>
+      <c r="BE49" t="inlineStr"/>
+      <c r="BF49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6171,7 +6330,7 @@
           <t>2024-12-09T00:00:00</t>
         </is>
       </c>
-      <c r="X50" t="b">
+      <c r="X50" t="n">
         <v>0</v>
       </c>
       <c r="Y50" t="inlineStr"/>
@@ -6205,6 +6364,9 @@
       <c r="BA50" t="inlineStr"/>
       <c r="BB50" t="inlineStr"/>
       <c r="BC50" t="inlineStr"/>
+      <c r="BD50" t="inlineStr"/>
+      <c r="BE50" t="inlineStr"/>
+      <c r="BF50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6300,7 +6462,7 @@
           <t>2021-07-01T00:00:00</t>
         </is>
       </c>
-      <c r="X51" t="b">
+      <c r="X51" t="n">
         <v>1</v>
       </c>
       <c r="Y51" t="inlineStr"/>
@@ -6334,6 +6496,9 @@
       <c r="BA51" t="inlineStr"/>
       <c r="BB51" t="inlineStr"/>
       <c r="BC51" t="inlineStr"/>
+      <c r="BD51" t="inlineStr"/>
+      <c r="BE51" t="inlineStr"/>
+      <c r="BF51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6433,7 +6598,7 @@
           <t>2022-01-17T00:00:00</t>
         </is>
       </c>
-      <c r="X52" t="b">
+      <c r="X52" t="n">
         <v>0</v>
       </c>
       <c r="Y52" t="inlineStr"/>
@@ -6467,6 +6632,9 @@
       <c r="BA52" t="inlineStr"/>
       <c r="BB52" t="inlineStr"/>
       <c r="BC52" t="inlineStr"/>
+      <c r="BD52" t="inlineStr"/>
+      <c r="BE52" t="inlineStr"/>
+      <c r="BF52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6566,7 +6734,7 @@
           <t>2022-09-22T00:00:00</t>
         </is>
       </c>
-      <c r="X53" t="b">
+      <c r="X53" t="n">
         <v>0</v>
       </c>
       <c r="Y53" t="inlineStr"/>
@@ -6600,6 +6768,9 @@
       <c r="BA53" t="inlineStr"/>
       <c r="BB53" t="inlineStr"/>
       <c r="BC53" t="inlineStr"/>
+      <c r="BD53" t="inlineStr"/>
+      <c r="BE53" t="inlineStr"/>
+      <c r="BF53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6683,7 +6854,7 @@
           <t>2026-06-30T00:00:00</t>
         </is>
       </c>
-      <c r="X54" t="b">
+      <c r="X54" t="n">
         <v>0</v>
       </c>
       <c r="Y54" t="inlineStr"/>
@@ -6717,6 +6888,9 @@
       <c r="BA54" t="inlineStr"/>
       <c r="BB54" t="inlineStr"/>
       <c r="BC54" t="inlineStr"/>
+      <c r="BD54" t="inlineStr"/>
+      <c r="BE54" t="inlineStr"/>
+      <c r="BF54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6796,7 +6970,7 @@
           <t>2030-05-01T00:00:00</t>
         </is>
       </c>
-      <c r="X55" t="b">
+      <c r="X55" t="n">
         <v>0</v>
       </c>
       <c r="Y55" t="inlineStr"/>
@@ -6830,6 +7004,9 @@
       <c r="BA55" t="inlineStr"/>
       <c r="BB55" t="inlineStr"/>
       <c r="BC55" t="inlineStr"/>
+      <c r="BD55" t="inlineStr"/>
+      <c r="BE55" t="inlineStr"/>
+      <c r="BF55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6913,7 +7090,7 @@
           <t>2029-05-01T00:00:00</t>
         </is>
       </c>
-      <c r="X56" t="b">
+      <c r="X56" t="n">
         <v>0</v>
       </c>
       <c r="Y56" t="inlineStr"/>
@@ -6947,6 +7124,9 @@
       <c r="BA56" t="inlineStr"/>
       <c r="BB56" t="inlineStr"/>
       <c r="BC56" t="inlineStr"/>
+      <c r="BD56" t="inlineStr"/>
+      <c r="BE56" t="inlineStr"/>
+      <c r="BF56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -7026,7 +7206,7 @@
           <t>2033-05-01T00:00:00</t>
         </is>
       </c>
-      <c r="X57" t="b">
+      <c r="X57" t="n">
         <v>0</v>
       </c>
       <c r="Y57" t="inlineStr"/>
@@ -7060,6 +7240,9 @@
       <c r="BA57" t="inlineStr"/>
       <c r="BB57" t="inlineStr"/>
       <c r="BC57" t="inlineStr"/>
+      <c r="BD57" t="inlineStr"/>
+      <c r="BE57" t="inlineStr"/>
+      <c r="BF57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -7139,7 +7322,7 @@
           <t>2029-05-01T00:00:00</t>
         </is>
       </c>
-      <c r="X58" t="b">
+      <c r="X58" t="n">
         <v>0</v>
       </c>
       <c r="Y58" t="inlineStr"/>
@@ -7173,6 +7356,9 @@
       <c r="BA58" t="inlineStr"/>
       <c r="BB58" t="inlineStr"/>
       <c r="BC58" t="inlineStr"/>
+      <c r="BD58" t="inlineStr"/>
+      <c r="BE58" t="inlineStr"/>
+      <c r="BF58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -7272,7 +7458,7 @@
           <t>2026-09-01T00:00:00</t>
         </is>
       </c>
-      <c r="X59" t="b">
+      <c r="X59" t="n">
         <v>0</v>
       </c>
       <c r="Y59" t="inlineStr"/>
@@ -7306,6 +7492,9 @@
       <c r="BA59" t="inlineStr"/>
       <c r="BB59" t="inlineStr"/>
       <c r="BC59" t="inlineStr"/>
+      <c r="BD59" t="inlineStr"/>
+      <c r="BE59" t="inlineStr"/>
+      <c r="BF59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -7403,7 +7592,7 @@
           <t>TBD</t>
         </is>
       </c>
-      <c r="X60" t="b">
+      <c r="X60" t="n">
         <v>0</v>
       </c>
       <c r="Y60" t="inlineStr"/>
@@ -7437,6 +7626,9 @@
       <c r="BA60" t="inlineStr"/>
       <c r="BB60" t="inlineStr"/>
       <c r="BC60" t="inlineStr"/>
+      <c r="BD60" t="inlineStr"/>
+      <c r="BE60" t="inlineStr"/>
+      <c r="BF60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -7532,7 +7724,7 @@
           <t>2031-09-23T00:00:00</t>
         </is>
       </c>
-      <c r="X61" t="b">
+      <c r="X61" t="n">
         <v>0</v>
       </c>
       <c r="Y61" t="inlineStr"/>
@@ -7566,6 +7758,9 @@
       <c r="BA61" t="inlineStr"/>
       <c r="BB61" t="inlineStr"/>
       <c r="BC61" t="inlineStr"/>
+      <c r="BD61" t="inlineStr"/>
+      <c r="BE61" t="inlineStr"/>
+      <c r="BF61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -7641,7 +7836,7 @@
           <t>2021-06-01T00:00:00</t>
         </is>
       </c>
-      <c r="X62" t="b">
+      <c r="X62" t="n">
         <v>0</v>
       </c>
       <c r="Y62" t="inlineStr"/>
@@ -7675,6 +7870,9 @@
       <c r="BA62" t="inlineStr"/>
       <c r="BB62" t="inlineStr"/>
       <c r="BC62" t="inlineStr"/>
+      <c r="BD62" t="inlineStr"/>
+      <c r="BE62" t="inlineStr"/>
+      <c r="BF62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -7770,7 +7968,7 @@
           <t>2022-09-22 00:00:00</t>
         </is>
       </c>
-      <c r="X63" t="b">
+      <c r="X63" t="n">
         <v>1</v>
       </c>
       <c r="Y63" t="inlineStr">
@@ -7814,6 +8012,9 @@
       <c r="BA63" t="inlineStr"/>
       <c r="BB63" t="inlineStr"/>
       <c r="BC63" t="inlineStr"/>
+      <c r="BD63" t="inlineStr"/>
+      <c r="BE63" t="inlineStr"/>
+      <c r="BF63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -7885,7 +8086,7 @@
       <c r="U64" t="inlineStr"/>
       <c r="V64" t="inlineStr"/>
       <c r="W64" t="inlineStr"/>
-      <c r="X64" t="b">
+      <c r="X64" t="n">
         <v>0</v>
       </c>
       <c r="Y64" t="inlineStr">
@@ -7929,6 +8130,9 @@
       <c r="BA64" t="inlineStr"/>
       <c r="BB64" t="inlineStr"/>
       <c r="BC64" t="inlineStr"/>
+      <c r="BD64" t="inlineStr"/>
+      <c r="BE64" t="inlineStr"/>
+      <c r="BF64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -8020,7 +8224,7 @@
           <t>2018-10-16 00:00:00</t>
         </is>
       </c>
-      <c r="X65" t="b">
+      <c r="X65" t="n">
         <v>1</v>
       </c>
       <c r="Y65" t="inlineStr">
@@ -8064,6 +8268,9 @@
       <c r="BA65" t="inlineStr"/>
       <c r="BB65" t="inlineStr"/>
       <c r="BC65" t="inlineStr"/>
+      <c r="BD65" t="inlineStr"/>
+      <c r="BE65" t="inlineStr"/>
+      <c r="BF65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -8139,7 +8346,7 @@
       <c r="U66" t="inlineStr"/>
       <c r="V66" t="inlineStr"/>
       <c r="W66" t="inlineStr"/>
-      <c r="X66" t="b">
+      <c r="X66" t="n">
         <v>1</v>
       </c>
       <c r="Y66" t="inlineStr">
@@ -8183,6 +8390,9 @@
       <c r="BA66" t="inlineStr"/>
       <c r="BB66" t="inlineStr"/>
       <c r="BC66" t="inlineStr"/>
+      <c r="BD66" t="inlineStr"/>
+      <c r="BE66" t="inlineStr"/>
+      <c r="BF66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -8258,7 +8468,7 @@
       <c r="U67" t="inlineStr"/>
       <c r="V67" t="inlineStr"/>
       <c r="W67" t="inlineStr"/>
-      <c r="X67" t="b">
+      <c r="X67" t="n">
         <v>0</v>
       </c>
       <c r="Y67" t="inlineStr">
@@ -8302,6 +8512,9 @@
       <c r="BA67" t="inlineStr"/>
       <c r="BB67" t="inlineStr"/>
       <c r="BC67" t="inlineStr"/>
+      <c r="BD67" t="inlineStr"/>
+      <c r="BE67" t="inlineStr"/>
+      <c r="BF67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -8386,7 +8599,7 @@
           <t>2023-06-15 00:00:00</t>
         </is>
       </c>
-      <c r="X68" t="b">
+      <c r="X68" t="n">
         <v>0</v>
       </c>
       <c r="Y68" t="inlineStr">
@@ -8431,6 +8644,9 @@
       <c r="BA68" t="inlineStr"/>
       <c r="BB68" t="inlineStr"/>
       <c r="BC68" t="inlineStr"/>
+      <c r="BD68" t="inlineStr"/>
+      <c r="BE68" t="inlineStr"/>
+      <c r="BF68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -8515,7 +8731,7 @@
           <t>2022-04-19 00:00:00</t>
         </is>
       </c>
-      <c r="X69" t="b">
+      <c r="X69" t="n">
         <v>0</v>
       </c>
       <c r="Y69" t="inlineStr">
@@ -8560,6 +8776,9 @@
       <c r="BA69" t="inlineStr"/>
       <c r="BB69" t="inlineStr"/>
       <c r="BC69" t="inlineStr"/>
+      <c r="BD69" t="inlineStr"/>
+      <c r="BE69" t="inlineStr"/>
+      <c r="BF69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -8631,7 +8850,7 @@
       <c r="U70" t="inlineStr"/>
       <c r="V70" t="inlineStr"/>
       <c r="W70" t="inlineStr"/>
-      <c r="X70" t="b">
+      <c r="X70" t="n">
         <v>1</v>
       </c>
       <c r="Y70" t="inlineStr">
@@ -8675,6 +8894,9 @@
       <c r="BA70" t="inlineStr"/>
       <c r="BB70" t="inlineStr"/>
       <c r="BC70" t="inlineStr"/>
+      <c r="BD70" t="inlineStr"/>
+      <c r="BE70" t="inlineStr"/>
+      <c r="BF70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -8767,7 +8989,7 @@
           <t>2021-07-26 00:00:00</t>
         </is>
       </c>
-      <c r="X71" t="b">
+      <c r="X71" t="n">
         <v>1</v>
       </c>
       <c r="Y71" t="inlineStr">
@@ -8812,6 +9034,9 @@
       <c r="BA71" t="inlineStr"/>
       <c r="BB71" t="inlineStr"/>
       <c r="BC71" t="inlineStr"/>
+      <c r="BD71" t="inlineStr"/>
+      <c r="BE71" t="inlineStr"/>
+      <c r="BF71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -8883,7 +9108,7 @@
           <t>2029-05-01 00:00:00</t>
         </is>
       </c>
-      <c r="X72" t="b">
+      <c r="X72" t="n">
         <v>0</v>
       </c>
       <c r="Y72" t="inlineStr">
@@ -8927,6 +9152,9 @@
       <c r="BA72" t="inlineStr"/>
       <c r="BB72" t="inlineStr"/>
       <c r="BC72" t="inlineStr"/>
+      <c r="BD72" t="inlineStr"/>
+      <c r="BE72" t="inlineStr"/>
+      <c r="BF72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -9014,7 +9242,7 @@
           <t>2030-09-10 00:00:00</t>
         </is>
       </c>
-      <c r="X73" t="b">
+      <c r="X73" t="n">
         <v>0</v>
       </c>
       <c r="Y73" t="inlineStr">
@@ -9058,6 +9286,9 @@
       <c r="BA73" t="inlineStr"/>
       <c r="BB73" t="inlineStr"/>
       <c r="BC73" t="inlineStr"/>
+      <c r="BD73" t="inlineStr"/>
+      <c r="BE73" t="inlineStr"/>
+      <c r="BF73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -9141,7 +9372,7 @@
           <t>2024-12-06 00:00:00</t>
         </is>
       </c>
-      <c r="X74" t="b">
+      <c r="X74" t="n">
         <v>0</v>
       </c>
       <c r="Y74" t="inlineStr">
@@ -9185,6 +9416,9 @@
       <c r="BA74" t="inlineStr"/>
       <c r="BB74" t="inlineStr"/>
       <c r="BC74" t="inlineStr"/>
+      <c r="BD74" t="inlineStr"/>
+      <c r="BE74" t="inlineStr"/>
+      <c r="BF74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -9272,7 +9506,7 @@
           <t>2025-03-24 00:00:00</t>
         </is>
       </c>
-      <c r="X75" t="b">
+      <c r="X75" t="n">
         <v>0</v>
       </c>
       <c r="Y75" t="inlineStr">
@@ -9316,6 +9550,9 @@
       <c r="BA75" t="inlineStr"/>
       <c r="BB75" t="inlineStr"/>
       <c r="BC75" t="inlineStr"/>
+      <c r="BD75" t="inlineStr"/>
+      <c r="BE75" t="inlineStr"/>
+      <c r="BF75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -9403,7 +9640,7 @@
           <t>2027-05-04 00:00:00</t>
         </is>
       </c>
-      <c r="X76" t="b">
+      <c r="X76" t="n">
         <v>0</v>
       </c>
       <c r="Y76" t="inlineStr">
@@ -9447,6 +9684,9 @@
       <c r="BA76" t="inlineStr"/>
       <c r="BB76" t="inlineStr"/>
       <c r="BC76" t="inlineStr"/>
+      <c r="BD76" t="inlineStr"/>
+      <c r="BE76" t="inlineStr"/>
+      <c r="BF76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -9518,7 +9758,7 @@
           <t>2029-05-01 00:00:00</t>
         </is>
       </c>
-      <c r="X77" t="b">
+      <c r="X77" t="n">
         <v>0</v>
       </c>
       <c r="Y77" t="inlineStr">
@@ -9562,6 +9802,9 @@
       <c r="BA77" t="inlineStr"/>
       <c r="BB77" t="inlineStr"/>
       <c r="BC77" t="inlineStr"/>
+      <c r="BD77" t="inlineStr"/>
+      <c r="BE77" t="inlineStr"/>
+      <c r="BF77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -9645,7 +9888,7 @@
           <t>2027-04-02 00:00:00</t>
         </is>
       </c>
-      <c r="X78" t="b">
+      <c r="X78" t="n">
         <v>0</v>
       </c>
       <c r="Y78" t="inlineStr">
@@ -9689,6 +9932,9 @@
       <c r="BA78" t="inlineStr"/>
       <c r="BB78" t="inlineStr"/>
       <c r="BC78" t="inlineStr"/>
+      <c r="BD78" t="inlineStr"/>
+      <c r="BE78" t="inlineStr"/>
+      <c r="BF78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -9776,7 +10022,7 @@
           <t>2027-07-20 00:00:00</t>
         </is>
       </c>
-      <c r="X79" t="b">
+      <c r="X79" t="n">
         <v>0</v>
       </c>
       <c r="Y79" t="inlineStr">
@@ -9820,6 +10066,9 @@
       <c r="BA79" t="inlineStr"/>
       <c r="BB79" t="inlineStr"/>
       <c r="BC79" t="inlineStr"/>
+      <c r="BD79" t="inlineStr"/>
+      <c r="BE79" t="inlineStr"/>
+      <c r="BF79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -9907,7 +10156,7 @@
           <t>2027-01-08 00:00:00</t>
         </is>
       </c>
-      <c r="X80" t="b">
+      <c r="X80" t="n">
         <v>0</v>
       </c>
       <c r="Y80" t="inlineStr">
@@ -9951,6 +10200,9 @@
       <c r="BA80" t="inlineStr"/>
       <c r="BB80" t="inlineStr"/>
       <c r="BC80" t="inlineStr"/>
+      <c r="BD80" t="inlineStr"/>
+      <c r="BE80" t="inlineStr"/>
+      <c r="BF80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -10038,7 +10290,7 @@
           <t>2027-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="X81" t="b">
+      <c r="X81" t="n">
         <v>0</v>
       </c>
       <c r="Y81" t="inlineStr">
@@ -10082,6 +10334,9 @@
       <c r="BA81" t="inlineStr"/>
       <c r="BB81" t="inlineStr"/>
       <c r="BC81" t="inlineStr"/>
+      <c r="BD81" t="inlineStr"/>
+      <c r="BE81" t="inlineStr"/>
+      <c r="BF81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -10165,7 +10420,7 @@
           <t>2026-07-01 00:00:00</t>
         </is>
       </c>
-      <c r="X82" t="b">
+      <c r="X82" t="n">
         <v>0</v>
       </c>
       <c r="Y82" t="inlineStr">
@@ -10209,6 +10464,9 @@
       <c r="BA82" t="inlineStr"/>
       <c r="BB82" t="inlineStr"/>
       <c r="BC82" t="inlineStr"/>
+      <c r="BD82" t="inlineStr"/>
+      <c r="BE82" t="inlineStr"/>
+      <c r="BF82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -10292,7 +10550,7 @@
           <t>2027-07-08 00:00:00</t>
         </is>
       </c>
-      <c r="X83" t="b">
+      <c r="X83" t="n">
         <v>0</v>
       </c>
       <c r="Y83" t="inlineStr">
@@ -10336,6 +10594,9 @@
       <c r="BA83" t="inlineStr"/>
       <c r="BB83" t="inlineStr"/>
       <c r="BC83" t="inlineStr"/>
+      <c r="BD83" t="inlineStr"/>
+      <c r="BE83" t="inlineStr"/>
+      <c r="BF83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -10415,7 +10676,7 @@
           <t>2029-05-01 00:00:00</t>
         </is>
       </c>
-      <c r="X84" t="b">
+      <c r="X84" t="n">
         <v>1</v>
       </c>
       <c r="Y84" t="inlineStr">
@@ -10459,6 +10720,9 @@
       <c r="BA84" t="inlineStr"/>
       <c r="BB84" t="inlineStr"/>
       <c r="BC84" t="inlineStr"/>
+      <c r="BD84" t="inlineStr"/>
+      <c r="BE84" t="inlineStr"/>
+      <c r="BF84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -10542,7 +10806,7 @@
           <t>2026-12-16 00:00:00</t>
         </is>
       </c>
-      <c r="X85" t="b">
+      <c r="X85" t="n">
         <v>0</v>
       </c>
       <c r="Y85" t="inlineStr">
@@ -10586,6 +10850,9 @@
       <c r="BA85" t="inlineStr"/>
       <c r="BB85" t="inlineStr"/>
       <c r="BC85" t="inlineStr"/>
+      <c r="BD85" t="inlineStr"/>
+      <c r="BE85" t="inlineStr"/>
+      <c r="BF85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -10681,7 +10948,7 @@
           <t>2027-10-12 00:00:00</t>
         </is>
       </c>
-      <c r="X86" t="b">
+      <c r="X86" t="n">
         <v>1</v>
       </c>
       <c r="Y86" t="inlineStr">
@@ -10725,6 +10992,9 @@
       <c r="BA86" t="inlineStr"/>
       <c r="BB86" t="inlineStr"/>
       <c r="BC86" t="inlineStr"/>
+      <c r="BD86" t="inlineStr"/>
+      <c r="BE86" t="inlineStr"/>
+      <c r="BF86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -10820,7 +11090,7 @@
           <t>2018-11-01 00:00:00</t>
         </is>
       </c>
-      <c r="X87" t="b">
+      <c r="X87" t="n">
         <v>1</v>
       </c>
       <c r="Y87" t="inlineStr">
@@ -10864,6 +11134,9 @@
       <c r="BA87" t="inlineStr"/>
       <c r="BB87" t="inlineStr"/>
       <c r="BC87" t="inlineStr"/>
+      <c r="BD87" t="inlineStr"/>
+      <c r="BE87" t="inlineStr"/>
+      <c r="BF87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -10955,7 +11228,7 @@
           <t>2021-04-07 00:00:00</t>
         </is>
       </c>
-      <c r="X88" t="b">
+      <c r="X88" t="n">
         <v>1</v>
       </c>
       <c r="Y88" t="inlineStr">
@@ -10999,6 +11272,9 @@
       <c r="BA88" t="inlineStr"/>
       <c r="BB88" t="inlineStr"/>
       <c r="BC88" t="inlineStr"/>
+      <c r="BD88" t="inlineStr"/>
+      <c r="BE88" t="inlineStr"/>
+      <c r="BF88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -11090,7 +11366,7 @@
           <t>2024-08-21 00:00:00</t>
         </is>
       </c>
-      <c r="X89" t="b">
+      <c r="X89" t="n">
         <v>1</v>
       </c>
       <c r="Y89" t="inlineStr">
@@ -11134,6 +11410,9 @@
       <c r="BA89" t="inlineStr"/>
       <c r="BB89" t="inlineStr"/>
       <c r="BC89" t="inlineStr"/>
+      <c r="BD89" t="inlineStr"/>
+      <c r="BE89" t="inlineStr"/>
+      <c r="BF89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -11221,7 +11500,7 @@
           <t>2027-03-11 00:00:00</t>
         </is>
       </c>
-      <c r="X90" t="b">
+      <c r="X90" t="n">
         <v>0</v>
       </c>
       <c r="Y90" t="inlineStr">
@@ -11265,6 +11544,9 @@
       <c r="BA90" t="inlineStr"/>
       <c r="BB90" t="inlineStr"/>
       <c r="BC90" t="inlineStr"/>
+      <c r="BD90" t="inlineStr"/>
+      <c r="BE90" t="inlineStr"/>
+      <c r="BF90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -11336,7 +11618,7 @@
           <t>2033-05-01 00:00:00</t>
         </is>
       </c>
-      <c r="X91" t="b">
+      <c r="X91" t="n">
         <v>0</v>
       </c>
       <c r="Y91" t="inlineStr">
@@ -11380,6 +11662,9 @@
       <c r="BA91" t="inlineStr"/>
       <c r="BB91" t="inlineStr"/>
       <c r="BC91" t="inlineStr"/>
+      <c r="BD91" t="inlineStr"/>
+      <c r="BE91" t="inlineStr"/>
+      <c r="BF91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -11459,7 +11744,7 @@
           <t>2033-05-01 00:00:00</t>
         </is>
       </c>
-      <c r="X92" t="b">
+      <c r="X92" t="n">
         <v>1</v>
       </c>
       <c r="Y92" t="inlineStr">
@@ -11503,6 +11788,9 @@
       <c r="BA92" t="inlineStr"/>
       <c r="BB92" t="inlineStr"/>
       <c r="BC92" t="inlineStr"/>
+      <c r="BD92" t="inlineStr"/>
+      <c r="BE92" t="inlineStr"/>
+      <c r="BF92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -11574,7 +11862,7 @@
           <t>2033-05-01 00:00:00</t>
         </is>
       </c>
-      <c r="X93" t="b">
+      <c r="X93" t="n">
         <v>0</v>
       </c>
       <c r="Y93" t="inlineStr">
@@ -11618,6 +11906,9 @@
       <c r="BA93" t="inlineStr"/>
       <c r="BB93" t="inlineStr"/>
       <c r="BC93" t="inlineStr"/>
+      <c r="BD93" t="inlineStr"/>
+      <c r="BE93" t="inlineStr"/>
+      <c r="BF93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -11706,7 +11997,7 @@
           <t>2028-07-28 00:00:00</t>
         </is>
       </c>
-      <c r="X94" t="b">
+      <c r="X94" t="n">
         <v>0</v>
       </c>
       <c r="Y94" t="inlineStr">
@@ -11751,6 +12042,9 @@
       <c r="BA94" t="inlineStr"/>
       <c r="BB94" t="inlineStr"/>
       <c r="BC94" t="inlineStr"/>
+      <c r="BD94" t="inlineStr"/>
+      <c r="BE94" t="inlineStr"/>
+      <c r="BF94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -11846,7 +12140,7 @@
           <t>2026-09-16 00:00:00</t>
         </is>
       </c>
-      <c r="X95" t="b">
+      <c r="X95" t="n">
         <v>1</v>
       </c>
       <c r="Y95" t="inlineStr">
@@ -11890,6 +12184,9 @@
       <c r="BA95" t="inlineStr"/>
       <c r="BB95" t="inlineStr"/>
       <c r="BC95" t="inlineStr"/>
+      <c r="BD95" t="inlineStr"/>
+      <c r="BE95" t="inlineStr"/>
+      <c r="BF95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -11977,7 +12274,7 @@
           <t>2027-09-15 00:00:00</t>
         </is>
       </c>
-      <c r="X96" t="b">
+      <c r="X96" t="n">
         <v>0</v>
       </c>
       <c r="Y96" t="inlineStr">
@@ -12021,6 +12318,9 @@
       <c r="BA96" t="inlineStr"/>
       <c r="BB96" t="inlineStr"/>
       <c r="BC96" t="inlineStr"/>
+      <c r="BD96" t="inlineStr"/>
+      <c r="BE96" t="inlineStr"/>
+      <c r="BF96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -12104,7 +12404,7 @@
           <t>2026-04-20 00:00:00</t>
         </is>
       </c>
-      <c r="X97" t="b">
+      <c r="X97" t="n">
         <v>0</v>
       </c>
       <c r="Y97" t="inlineStr">
@@ -12148,6 +12448,9 @@
       <c r="BA97" t="inlineStr"/>
       <c r="BB97" t="inlineStr"/>
       <c r="BC97" t="inlineStr"/>
+      <c r="BD97" t="inlineStr"/>
+      <c r="BE97" t="inlineStr"/>
+      <c r="BF97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -12243,7 +12546,7 @@
           <t>2026-07-22 00:00:00</t>
         </is>
       </c>
-      <c r="X98" t="b">
+      <c r="X98" t="n">
         <v>1</v>
       </c>
       <c r="Y98" t="inlineStr">
@@ -12287,6 +12590,9 @@
       <c r="BA98" t="inlineStr"/>
       <c r="BB98" t="inlineStr"/>
       <c r="BC98" t="inlineStr"/>
+      <c r="BD98" t="inlineStr"/>
+      <c r="BE98" t="inlineStr"/>
+      <c r="BF98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -12370,7 +12676,7 @@
           <t>2027-03-10 00:00:00</t>
         </is>
       </c>
-      <c r="X99" t="b">
+      <c r="X99" t="n">
         <v>0</v>
       </c>
       <c r="Y99" t="inlineStr">
@@ -12414,6 +12720,9 @@
       <c r="BA99" t="inlineStr"/>
       <c r="BB99" t="inlineStr"/>
       <c r="BC99" t="inlineStr"/>
+      <c r="BD99" t="inlineStr"/>
+      <c r="BE99" t="inlineStr"/>
+      <c r="BF99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -12485,7 +12794,7 @@
           <t>2029-05-01 00:00:00</t>
         </is>
       </c>
-      <c r="X100" t="b">
+      <c r="X100" t="n">
         <v>0</v>
       </c>
       <c r="Y100" t="inlineStr">
@@ -12529,6 +12838,9 @@
       <c r="BA100" t="inlineStr"/>
       <c r="BB100" t="inlineStr"/>
       <c r="BC100" t="inlineStr"/>
+      <c r="BD100" t="inlineStr"/>
+      <c r="BE100" t="inlineStr"/>
+      <c r="BF100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -12600,7 +12912,7 @@
           <t>2029-12-01 00:00:00</t>
         </is>
       </c>
-      <c r="X101" t="b">
+      <c r="X101" t="n">
         <v>0</v>
       </c>
       <c r="Y101" t="inlineStr">
@@ -12644,6 +12956,9 @@
       <c r="BA101" t="inlineStr"/>
       <c r="BB101" t="inlineStr"/>
       <c r="BC101" t="inlineStr"/>
+      <c r="BD101" t="inlineStr"/>
+      <c r="BE101" t="inlineStr"/>
+      <c r="BF101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -12731,7 +13046,7 @@
           <t>2025-10-17 00:00:00</t>
         </is>
       </c>
-      <c r="X102" t="b">
+      <c r="X102" t="n">
         <v>0</v>
       </c>
       <c r="Y102" t="inlineStr">
@@ -12775,6 +13090,9 @@
       <c r="BA102" t="inlineStr"/>
       <c r="BB102" t="inlineStr"/>
       <c r="BC102" t="inlineStr"/>
+      <c r="BD102" t="inlineStr"/>
+      <c r="BE102" t="inlineStr"/>
+      <c r="BF102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -12862,7 +13180,7 @@
           <t>2025-05-05 00:00:00</t>
         </is>
       </c>
-      <c r="X103" t="b">
+      <c r="X103" t="n">
         <v>0</v>
       </c>
       <c r="Y103" t="inlineStr">
@@ -12906,6 +13224,9 @@
       <c r="BA103" t="inlineStr"/>
       <c r="BB103" t="inlineStr"/>
       <c r="BC103" t="inlineStr"/>
+      <c r="BD103" t="inlineStr"/>
+      <c r="BE103" t="inlineStr"/>
+      <c r="BF103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -12993,7 +13314,7 @@
           <t>2025-06-13 00:00:00</t>
         </is>
       </c>
-      <c r="X104" t="b">
+      <c r="X104" t="n">
         <v>0</v>
       </c>
       <c r="Y104" t="inlineStr">
@@ -13037,6 +13358,9 @@
       <c r="BA104" t="inlineStr"/>
       <c r="BB104" t="inlineStr"/>
       <c r="BC104" t="inlineStr"/>
+      <c r="BD104" t="inlineStr"/>
+      <c r="BE104" t="inlineStr"/>
+      <c r="BF104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -13120,7 +13444,7 @@
           <t>2024-06-01 00:00:00</t>
         </is>
       </c>
-      <c r="X105" t="b">
+      <c r="X105" t="n">
         <v>0</v>
       </c>
       <c r="Y105" t="inlineStr">
@@ -13164,6 +13488,9 @@
       <c r="BA105" t="inlineStr"/>
       <c r="BB105" t="inlineStr"/>
       <c r="BC105" t="inlineStr"/>
+      <c r="BD105" t="inlineStr"/>
+      <c r="BE105" t="inlineStr"/>
+      <c r="BF105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -13251,7 +13578,7 @@
           <t>2027-11-15 00:00:00</t>
         </is>
       </c>
-      <c r="X106" t="b">
+      <c r="X106" t="n">
         <v>0</v>
       </c>
       <c r="Y106" t="inlineStr">
@@ -13295,6 +13622,9 @@
       <c r="BA106" t="inlineStr"/>
       <c r="BB106" t="inlineStr"/>
       <c r="BC106" t="inlineStr"/>
+      <c r="BD106" t="inlineStr"/>
+      <c r="BE106" t="inlineStr"/>
+      <c r="BF106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -13366,7 +13696,7 @@
           <t>2026-08-01 00:00:00</t>
         </is>
       </c>
-      <c r="X107" t="b">
+      <c r="X107" t="n">
         <v>0</v>
       </c>
       <c r="Y107" t="inlineStr">
@@ -13410,6 +13740,9 @@
       <c r="BA107" t="inlineStr"/>
       <c r="BB107" t="inlineStr"/>
       <c r="BC107" t="inlineStr"/>
+      <c r="BD107" t="inlineStr"/>
+      <c r="BE107" t="inlineStr"/>
+      <c r="BF107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -13493,7 +13826,7 @@
           <t>2024-05-13 00:00:00</t>
         </is>
       </c>
-      <c r="X108" t="b">
+      <c r="X108" t="n">
         <v>0</v>
       </c>
       <c r="Y108" t="inlineStr">
@@ -13537,6 +13870,9 @@
       <c r="BA108" t="inlineStr"/>
       <c r="BB108" t="inlineStr"/>
       <c r="BC108" t="inlineStr"/>
+      <c r="BD108" t="inlineStr"/>
+      <c r="BE108" t="inlineStr"/>
+      <c r="BF108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -13608,7 +13944,7 @@
           <t>2029-05-01 00:00:00</t>
         </is>
       </c>
-      <c r="X109" t="b">
+      <c r="X109" t="n">
         <v>0</v>
       </c>
       <c r="Y109" t="inlineStr">
@@ -13652,6 +13988,9 @@
       <c r="BA109" t="inlineStr"/>
       <c r="BB109" t="inlineStr"/>
       <c r="BC109" t="inlineStr"/>
+      <c r="BD109" t="inlineStr"/>
+      <c r="BE109" t="inlineStr"/>
+      <c r="BF109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -13739,7 +14078,7 @@
           <t>2026-04-27 00:00:00</t>
         </is>
       </c>
-      <c r="X110" t="b">
+      <c r="X110" t="n">
         <v>0</v>
       </c>
       <c r="Y110" t="inlineStr">
@@ -13783,6 +14122,9 @@
       <c r="BA110" t="inlineStr"/>
       <c r="BB110" t="inlineStr"/>
       <c r="BC110" t="inlineStr"/>
+      <c r="BD110" t="inlineStr"/>
+      <c r="BE110" t="inlineStr"/>
+      <c r="BF110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -13866,7 +14208,7 @@
           <t>2026-10-12 00:00:00</t>
         </is>
       </c>
-      <c r="X111" t="b">
+      <c r="X111" t="n">
         <v>0</v>
       </c>
       <c r="Y111" t="inlineStr">
@@ -13910,6 +14252,9 @@
       <c r="BA111" t="inlineStr"/>
       <c r="BB111" t="inlineStr"/>
       <c r="BC111" t="inlineStr"/>
+      <c r="BD111" t="inlineStr"/>
+      <c r="BE111" t="inlineStr"/>
+      <c r="BF111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -13956,10 +14301,8 @@
           <t>2009</t>
         </is>
       </c>
-      <c r="O112" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
+      <c r="O112" t="n">
+        <v>2014</v>
       </c>
       <c r="P112" t="inlineStr">
         <is>
@@ -13997,7 +14340,7 @@
           <t>2026-06-01 00:00:00</t>
         </is>
       </c>
-      <c r="X112" t="b">
+      <c r="X112" t="n">
         <v>0</v>
       </c>
       <c r="Y112" t="inlineStr">
@@ -14041,6 +14384,9 @@
       <c r="BA112" t="inlineStr"/>
       <c r="BB112" t="inlineStr"/>
       <c r="BC112" t="inlineStr"/>
+      <c r="BD112" t="inlineStr"/>
+      <c r="BE112" t="inlineStr"/>
+      <c r="BF112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -14087,10 +14433,8 @@
           <t>2021-2022</t>
         </is>
       </c>
-      <c r="O113" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="O113" t="n">
+        <v>2026</v>
       </c>
       <c r="P113" t="inlineStr"/>
       <c r="Q113" t="inlineStr">
@@ -14124,7 +14468,7 @@
           <t>2024-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="X113" t="b">
+      <c r="X113" t="n">
         <v>0</v>
       </c>
       <c r="Y113" t="inlineStr">
@@ -14168,6 +14512,9 @@
       <c r="BA113" t="inlineStr"/>
       <c r="BB113" t="inlineStr"/>
       <c r="BC113" t="inlineStr"/>
+      <c r="BD113" t="inlineStr"/>
+      <c r="BE113" t="inlineStr"/>
+      <c r="BF113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -14222,10 +14569,8 @@
           <t>2022-2023</t>
         </is>
       </c>
-      <c r="O114" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+      <c r="O114" t="n">
+        <v>2025</v>
       </c>
       <c r="P114" t="inlineStr"/>
       <c r="Q114" t="inlineStr">
@@ -14259,7 +14604,7 @@
           <t>2025-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="X114" t="b">
+      <c r="X114" t="n">
         <v>1</v>
       </c>
       <c r="Y114" t="inlineStr">
@@ -14303,6 +14648,9 @@
       <c r="BA114" t="inlineStr"/>
       <c r="BB114" t="inlineStr"/>
       <c r="BC114" t="inlineStr"/>
+      <c r="BD114" t="inlineStr"/>
+      <c r="BE114" t="inlineStr"/>
+      <c r="BF114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -14357,10 +14705,8 @@
           <t>2022-2023</t>
         </is>
       </c>
-      <c r="O115" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
+      <c r="O115" t="n">
+        <v>2028</v>
       </c>
       <c r="P115" t="inlineStr"/>
       <c r="Q115" t="inlineStr">
@@ -14394,7 +14740,7 @@
           <t>2025-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="X115" t="b">
+      <c r="X115" t="n">
         <v>1</v>
       </c>
       <c r="Y115" t="inlineStr">
@@ -14438,6 +14784,9 @@
       <c r="BA115" t="inlineStr"/>
       <c r="BB115" t="inlineStr"/>
       <c r="BC115" t="inlineStr"/>
+      <c r="BD115" t="inlineStr"/>
+      <c r="BE115" t="inlineStr"/>
+      <c r="BF115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -14484,10 +14833,8 @@
           <t>2021-2022</t>
         </is>
       </c>
-      <c r="O116" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="O116" t="n">
+        <v>2023</v>
       </c>
       <c r="P116" t="inlineStr"/>
       <c r="Q116" t="inlineStr">
@@ -14521,7 +14868,7 @@
           <t>2024-06-01 00:00:00</t>
         </is>
       </c>
-      <c r="X116" t="b">
+      <c r="X116" t="n">
         <v>0</v>
       </c>
       <c r="Y116" t="inlineStr">
@@ -14565,6 +14912,9 @@
       <c r="BA116" t="inlineStr"/>
       <c r="BB116" t="inlineStr"/>
       <c r="BC116" t="inlineStr"/>
+      <c r="BD116" t="inlineStr"/>
+      <c r="BE116" t="inlineStr"/>
+      <c r="BF116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -14619,10 +14969,8 @@
           <t>2022-2023</t>
         </is>
       </c>
-      <c r="O117" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
+      <c r="O117" t="n">
+        <v>2028</v>
       </c>
       <c r="P117" t="inlineStr"/>
       <c r="Q117" t="inlineStr">
@@ -14656,7 +15004,7 @@
           <t>2027-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="X117" t="b">
+      <c r="X117" t="n">
         <v>1</v>
       </c>
       <c r="Y117" t="inlineStr">
@@ -14700,6 +15048,9 @@
       <c r="BA117" t="inlineStr"/>
       <c r="BB117" t="inlineStr"/>
       <c r="BC117" t="inlineStr"/>
+      <c r="BD117" t="inlineStr"/>
+      <c r="BE117" t="inlineStr"/>
+      <c r="BF117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -14746,10 +15097,8 @@
           <t>2022-2023</t>
         </is>
       </c>
-      <c r="O118" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
+      <c r="O118" t="n">
+        <v>2028</v>
       </c>
       <c r="P118" t="inlineStr"/>
       <c r="Q118" t="inlineStr">
@@ -14783,7 +15132,7 @@
           <t>2026-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="X118" t="b">
+      <c r="X118" t="n">
         <v>0</v>
       </c>
       <c r="Y118" t="inlineStr">
@@ -14827,6 +15176,9 @@
       <c r="BA118" t="inlineStr"/>
       <c r="BB118" t="inlineStr"/>
       <c r="BC118" t="inlineStr"/>
+      <c r="BD118" t="inlineStr"/>
+      <c r="BE118" t="inlineStr"/>
+      <c r="BF118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -14881,10 +15233,8 @@
           <t>2021-2022</t>
         </is>
       </c>
-      <c r="O119" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="O119" t="n">
+        <v>2023</v>
       </c>
       <c r="P119" t="inlineStr"/>
       <c r="Q119" t="inlineStr">
@@ -14918,7 +15268,7 @@
           <t>Construction started</t>
         </is>
       </c>
-      <c r="X119" t="b">
+      <c r="X119" t="n">
         <v>1</v>
       </c>
       <c r="Y119" t="inlineStr">
@@ -14962,6 +15312,9 @@
       <c r="BA119" t="inlineStr"/>
       <c r="BB119" t="inlineStr"/>
       <c r="BC119" t="inlineStr"/>
+      <c r="BD119" t="inlineStr"/>
+      <c r="BE119" t="inlineStr"/>
+      <c r="BF119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -15008,10 +15361,8 @@
           <t>2012-2013</t>
         </is>
       </c>
-      <c r="O120" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
+      <c r="O120" t="n">
+        <v>2016</v>
       </c>
       <c r="P120" t="inlineStr">
         <is>
@@ -15049,7 +15400,7 @@
           <t>2020-12-01 00:00:00</t>
         </is>
       </c>
-      <c r="X120" t="b">
+      <c r="X120" t="n">
         <v>0</v>
       </c>
       <c r="Y120" t="inlineStr">
@@ -15093,6 +15444,9 @@
       <c r="BA120" t="inlineStr"/>
       <c r="BB120" t="inlineStr"/>
       <c r="BC120" t="inlineStr"/>
+      <c r="BD120" t="inlineStr"/>
+      <c r="BE120" t="inlineStr"/>
+      <c r="BF120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -15188,7 +15542,7 @@
           <t>Construction started</t>
         </is>
       </c>
-      <c r="X121" t="b">
+      <c r="X121" t="n">
         <v>1</v>
       </c>
       <c r="Y121" t="inlineStr">
@@ -15232,6 +15586,9 @@
       <c r="BA121" t="inlineStr"/>
       <c r="BB121" t="inlineStr"/>
       <c r="BC121" t="inlineStr"/>
+      <c r="BD121" t="inlineStr"/>
+      <c r="BE121" t="inlineStr"/>
+      <c r="BF121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -15289,10 +15646,8 @@
           <t>2022-2023</t>
         </is>
       </c>
-      <c r="O122" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
+      <c r="O122" t="n">
+        <v>2033</v>
       </c>
       <c r="P122" t="inlineStr"/>
       <c r="Q122" t="inlineStr">
@@ -15326,7 +15681,7 @@
           <t>1931-01-01 00:00:00</t>
         </is>
       </c>
-      <c r="X122" t="b">
+      <c r="X122" t="n">
         <v>1</v>
       </c>
       <c r="Y122" t="inlineStr">
@@ -15372,6 +15727,9 @@
       <c r="BA122" t="inlineStr"/>
       <c r="BB122" t="inlineStr"/>
       <c r="BC122" t="inlineStr"/>
+      <c r="BD122" t="inlineStr"/>
+      <c r="BE122" t="inlineStr"/>
+      <c r="BF122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -15418,10 +15776,8 @@
           <t>2022-2023</t>
         </is>
       </c>
-      <c r="O123" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="O123" t="n">
+        <v>2026</v>
       </c>
       <c r="P123" t="inlineStr"/>
       <c r="Q123" t="inlineStr">
@@ -15455,7 +15811,7 @@
           <t>2028-05-01 00:00:00</t>
         </is>
       </c>
-      <c r="X123" t="b">
+      <c r="X123" t="n">
         <v>0</v>
       </c>
       <c r="Y123" t="inlineStr">
@@ -15499,6 +15855,9 @@
       <c r="BA123" t="inlineStr"/>
       <c r="BB123" t="inlineStr"/>
       <c r="BC123" t="inlineStr"/>
+      <c r="BD123" t="inlineStr"/>
+      <c r="BE123" t="inlineStr"/>
+      <c r="BF123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -15545,10 +15904,8 @@
           <t>2022-2023</t>
         </is>
       </c>
-      <c r="O124" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="O124" t="n">
+        <v>2026</v>
       </c>
       <c r="P124" t="inlineStr"/>
       <c r="Q124" t="inlineStr">
@@ -15582,7 +15939,7 @@
           <t>2026-03-01 00:00:00</t>
         </is>
       </c>
-      <c r="X124" t="b">
+      <c r="X124" t="n">
         <v>0</v>
       </c>
       <c r="Y124" t="inlineStr">
@@ -15626,6 +15983,9 @@
       <c r="BA124" t="inlineStr"/>
       <c r="BB124" t="inlineStr"/>
       <c r="BC124" t="inlineStr"/>
+      <c r="BD124" t="inlineStr"/>
+      <c r="BE124" t="inlineStr"/>
+      <c r="BF124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -15672,10 +16032,8 @@
           <t>2022-2023</t>
         </is>
       </c>
-      <c r="O125" t="inlineStr">
-        <is>
-          <t>2027</t>
-        </is>
+      <c r="O125" t="n">
+        <v>2027</v>
       </c>
       <c r="P125" t="inlineStr"/>
       <c r="Q125" t="inlineStr">
@@ -15709,7 +16067,7 @@
           <t>2027-03-01 00:00:00</t>
         </is>
       </c>
-      <c r="X125" t="b">
+      <c r="X125" t="n">
         <v>0</v>
       </c>
       <c r="Y125" t="inlineStr">
@@ -15753,6 +16111,9 @@
       <c r="BA125" t="inlineStr"/>
       <c r="BB125" t="inlineStr"/>
       <c r="BC125" t="inlineStr"/>
+      <c r="BD125" t="inlineStr"/>
+      <c r="BE125" t="inlineStr"/>
+      <c r="BF125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -15840,7 +16201,7 @@
           <t>2027-01-01 00:00:00</t>
         </is>
       </c>
-      <c r="X126" t="b">
+      <c r="X126" t="n">
         <v>0</v>
       </c>
       <c r="Y126" t="inlineStr">
@@ -15884,6 +16245,9 @@
       <c r="BA126" t="inlineStr"/>
       <c r="BB126" t="inlineStr"/>
       <c r="BC126" t="inlineStr"/>
+      <c r="BD126" t="inlineStr"/>
+      <c r="BE126" t="inlineStr"/>
+      <c r="BF126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -15930,10 +16294,8 @@
           <t>2022-2023</t>
         </is>
       </c>
-      <c r="O127" t="inlineStr">
-        <is>
-          <t>2031</t>
-        </is>
+      <c r="O127" t="n">
+        <v>2031</v>
       </c>
       <c r="P127" t="inlineStr"/>
       <c r="Q127" t="inlineStr">
@@ -15967,7 +16329,7 @@
           <t>2026-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="X127" t="b">
+      <c r="X127" t="n">
         <v>0</v>
       </c>
       <c r="Y127" t="inlineStr">
@@ -16011,6 +16373,9 @@
       <c r="BA127" t="inlineStr"/>
       <c r="BB127" t="inlineStr"/>
       <c r="BC127" t="inlineStr"/>
+      <c r="BD127" t="inlineStr"/>
+      <c r="BE127" t="inlineStr"/>
+      <c r="BF127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -16057,10 +16422,8 @@
           <t>2022-2023</t>
         </is>
       </c>
-      <c r="O128" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
+      <c r="O128" t="n">
+        <v>2026</v>
       </c>
       <c r="P128" t="inlineStr"/>
       <c r="Q128" t="inlineStr">
@@ -16094,7 +16457,7 @@
           <t>2026-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="X128" t="b">
+      <c r="X128" t="n">
         <v>0</v>
       </c>
       <c r="Y128" t="inlineStr">
@@ -16138,6 +16501,9 @@
       <c r="BA128" t="inlineStr"/>
       <c r="BB128" t="inlineStr"/>
       <c r="BC128" t="inlineStr"/>
+      <c r="BD128" t="inlineStr"/>
+      <c r="BE128" t="inlineStr"/>
+      <c r="BF128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -16184,10 +16550,8 @@
           <t>2022-2023</t>
         </is>
       </c>
-      <c r="O129" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
+      <c r="O129" t="n">
+        <v>2028</v>
       </c>
       <c r="P129" t="inlineStr"/>
       <c r="Q129" t="inlineStr">
@@ -16221,7 +16585,7 @@
           <t>2027-03-01 00:00:00</t>
         </is>
       </c>
-      <c r="X129" t="b">
+      <c r="X129" t="n">
         <v>0</v>
       </c>
       <c r="Y129" t="inlineStr">
@@ -16265,6 +16629,9 @@
       <c r="BA129" t="inlineStr"/>
       <c r="BB129" t="inlineStr"/>
       <c r="BC129" t="inlineStr"/>
+      <c r="BD129" t="inlineStr"/>
+      <c r="BE129" t="inlineStr"/>
+      <c r="BF129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -16319,10 +16686,8 @@
           <t>2022-2023</t>
         </is>
       </c>
-      <c r="O130" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
+      <c r="O130" t="n">
+        <v>2033</v>
       </c>
       <c r="P130" t="inlineStr"/>
       <c r="Q130" t="inlineStr">
@@ -16356,7 +16721,7 @@
           <t>2031-01-01 00:00:00</t>
         </is>
       </c>
-      <c r="X130" t="b">
+      <c r="X130" t="n">
         <v>1</v>
       </c>
       <c r="Y130" t="inlineStr">
@@ -16400,6 +16765,9 @@
       <c r="BA130" t="inlineStr"/>
       <c r="BB130" t="inlineStr"/>
       <c r="BC130" t="inlineStr"/>
+      <c r="BD130" t="inlineStr"/>
+      <c r="BE130" t="inlineStr"/>
+      <c r="BF130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -16446,10 +16814,8 @@
           <t>2022-2023</t>
         </is>
       </c>
-      <c r="O131" t="inlineStr">
-        <is>
-          <t>2031</t>
-        </is>
+      <c r="O131" t="n">
+        <v>2031</v>
       </c>
       <c r="P131" t="inlineStr"/>
       <c r="Q131" t="inlineStr">
@@ -16483,7 +16849,7 @@
           <t>2026-10-01 00:00:00</t>
         </is>
       </c>
-      <c r="X131" t="b">
+      <c r="X131" t="n">
         <v>0</v>
       </c>
       <c r="Y131" t="inlineStr">
@@ -16527,6 +16893,9 @@
       <c r="BA131" t="inlineStr"/>
       <c r="BB131" t="inlineStr"/>
       <c r="BC131" t="inlineStr"/>
+      <c r="BD131" t="inlineStr"/>
+      <c r="BE131" t="inlineStr"/>
+      <c r="BF131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -16598,7 +16967,7 @@
           <t>2018-06-29 00:00:00</t>
         </is>
       </c>
-      <c r="X132" t="b">
+      <c r="X132" t="n">
         <v>0</v>
       </c>
       <c r="Y132" t="inlineStr">
@@ -16642,6 +17011,9 @@
       <c r="BA132" t="inlineStr"/>
       <c r="BB132" t="inlineStr"/>
       <c r="BC132" t="inlineStr"/>
+      <c r="BD132" t="inlineStr"/>
+      <c r="BE132" t="inlineStr"/>
+      <c r="BF132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -16721,7 +17093,7 @@
           <t>2025-10-03 00:00:00</t>
         </is>
       </c>
-      <c r="X133" t="b">
+      <c r="X133" t="n">
         <v>0</v>
       </c>
       <c r="Y133" t="inlineStr">
@@ -16765,6 +17137,9 @@
       <c r="BA133" t="inlineStr"/>
       <c r="BB133" t="inlineStr"/>
       <c r="BC133" t="inlineStr"/>
+      <c r="BD133" t="inlineStr"/>
+      <c r="BE133" t="inlineStr"/>
+      <c r="BF133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -16844,7 +17219,7 @@
           <t>2025-04-01 00:00:00</t>
         </is>
       </c>
-      <c r="X134" t="b">
+      <c r="X134" t="n">
         <v>0</v>
       </c>
       <c r="Y134" t="inlineStr">
@@ -16888,6 +17263,9 @@
       <c r="BA134" t="inlineStr"/>
       <c r="BB134" t="inlineStr"/>
       <c r="BC134" t="inlineStr"/>
+      <c r="BD134" t="inlineStr"/>
+      <c r="BE134" t="inlineStr"/>
+      <c r="BF134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -16975,7 +17353,7 @@
           <t>TBD</t>
         </is>
       </c>
-      <c r="X135" t="b">
+      <c r="X135" t="n">
         <v>1</v>
       </c>
       <c r="Y135" t="inlineStr">
@@ -17019,6 +17397,9 @@
       <c r="BA135" t="inlineStr"/>
       <c r="BB135" t="inlineStr"/>
       <c r="BC135" t="inlineStr"/>
+      <c r="BD135" t="inlineStr"/>
+      <c r="BE135" t="inlineStr"/>
+      <c r="BF135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -17106,7 +17487,7 @@
           <t>TBD</t>
         </is>
       </c>
-      <c r="X136" t="b">
+      <c r="X136" t="n">
         <v>1</v>
       </c>
       <c r="Y136" t="inlineStr">
@@ -17150,6 +17531,9 @@
       <c r="BA136" t="inlineStr"/>
       <c r="BB136" t="inlineStr"/>
       <c r="BC136" t="inlineStr"/>
+      <c r="BD136" t="inlineStr"/>
+      <c r="BE136" t="inlineStr"/>
+      <c r="BF136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -17221,7 +17605,7 @@
           <t>TBD</t>
         </is>
       </c>
-      <c r="X137" t="b">
+      <c r="X137" t="n">
         <v>0</v>
       </c>
       <c r="Y137" t="inlineStr">
@@ -17265,6 +17649,9 @@
       <c r="BA137" t="inlineStr"/>
       <c r="BB137" t="inlineStr"/>
       <c r="BC137" t="inlineStr"/>
+      <c r="BD137" t="inlineStr"/>
+      <c r="BE137" t="inlineStr"/>
+      <c r="BF137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -17336,7 +17723,7 @@
           <t>TBD</t>
         </is>
       </c>
-      <c r="X138" t="b">
+      <c r="X138" t="n">
         <v>0</v>
       </c>
       <c r="Y138" t="inlineStr">
@@ -17380,6 +17767,9 @@
       <c r="BA138" t="inlineStr"/>
       <c r="BB138" t="inlineStr"/>
       <c r="BC138" t="inlineStr"/>
+      <c r="BD138" t="inlineStr"/>
+      <c r="BE138" t="inlineStr"/>
+      <c r="BF138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -17459,7 +17849,7 @@
           <t>2026-01-01 00:00:00</t>
         </is>
       </c>
-      <c r="X139" t="b">
+      <c r="X139" t="n">
         <v>0</v>
       </c>
       <c r="Y139" t="inlineStr">
@@ -17503,6 +17893,9 @@
       <c r="BA139" t="inlineStr"/>
       <c r="BB139" t="inlineStr"/>
       <c r="BC139" t="inlineStr"/>
+      <c r="BD139" t="inlineStr"/>
+      <c r="BE139" t="inlineStr"/>
+      <c r="BF139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -17549,10 +17942,8 @@
           <t>2013-2014</t>
         </is>
       </c>
-      <c r="O140" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
+      <c r="O140" t="n">
+        <v>2020</v>
       </c>
       <c r="P140" t="inlineStr">
         <is>
@@ -17586,7 +17977,7 @@
           <t>2022-10-22</t>
         </is>
       </c>
-      <c r="X140" t="b">
+      <c r="X140" t="n">
         <v>0</v>
       </c>
       <c r="Y140" t="inlineStr">
@@ -17630,6 +18021,9 @@
       <c r="BA140" t="inlineStr"/>
       <c r="BB140" t="inlineStr"/>
       <c r="BC140" t="inlineStr"/>
+      <c r="BD140" t="inlineStr"/>
+      <c r="BE140" t="inlineStr"/>
+      <c r="BF140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -17691,7 +18085,7 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="X141" t="b">
+      <c r="X141" t="n">
         <v>0</v>
       </c>
       <c r="Y141" t="inlineStr">
@@ -17735,6 +18129,9 @@
       <c r="BA141" t="inlineStr"/>
       <c r="BB141" t="inlineStr"/>
       <c r="BC141" t="inlineStr"/>
+      <c r="BD141" t="inlineStr"/>
+      <c r="BE141" t="inlineStr"/>
+      <c r="BF141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -17772,7 +18169,7 @@
       <c r="U142" t="inlineStr"/>
       <c r="V142" t="inlineStr"/>
       <c r="W142" t="inlineStr"/>
-      <c r="X142" t="b">
+      <c r="X142" t="n">
         <v>0</v>
       </c>
       <c r="Y142" t="inlineStr">
@@ -17816,6 +18213,9 @@
       <c r="BA142" t="inlineStr"/>
       <c r="BB142" t="inlineStr"/>
       <c r="BC142" t="inlineStr"/>
+      <c r="BD142" t="inlineStr"/>
+      <c r="BE142" t="inlineStr"/>
+      <c r="BF142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -17868,25 +18268,17 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="Q143" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="R143" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="T143" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+      <c r="Q143" t="n">
+        <v>2023</v>
+      </c>
+      <c r="R143" t="n">
+        <v>2023</v>
+      </c>
+      <c r="S143" t="n">
+        <v>2023</v>
+      </c>
+      <c r="T143" t="n">
+        <v>2023</v>
       </c>
       <c r="U143" t="inlineStr"/>
       <c r="V143" t="inlineStr"/>
@@ -17895,7 +18287,7 @@
           <t>2023-07-21</t>
         </is>
       </c>
-      <c r="X143" t="b">
+      <c r="X143" t="n">
         <v>0</v>
       </c>
       <c r="Y143" t="inlineStr">
@@ -17939,6 +18331,9 @@
       <c r="BA143" t="inlineStr"/>
       <c r="BB143" t="inlineStr"/>
       <c r="BC143" t="inlineStr"/>
+      <c r="BD143" t="inlineStr"/>
+      <c r="BE143" t="inlineStr"/>
+      <c r="BF143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -17976,7 +18371,7 @@
       <c r="U144" t="inlineStr"/>
       <c r="V144" t="inlineStr"/>
       <c r="W144" t="inlineStr"/>
-      <c r="X144" t="b">
+      <c r="X144" t="n">
         <v>0</v>
       </c>
       <c r="Y144" t="inlineStr">
@@ -18020,6 +18415,9 @@
       <c r="BA144" t="inlineStr"/>
       <c r="BB144" t="inlineStr"/>
       <c r="BC144" t="inlineStr"/>
+      <c r="BD144" t="inlineStr"/>
+      <c r="BE144" t="inlineStr"/>
+      <c r="BF144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -18087,7 +18485,7 @@
           <t>2030-07-15</t>
         </is>
       </c>
-      <c r="X145" t="b">
+      <c r="X145" t="n">
         <v>0</v>
       </c>
       <c r="Y145" t="inlineStr">
@@ -18131,6 +18529,9 @@
       <c r="BA145" t="inlineStr"/>
       <c r="BB145" t="inlineStr"/>
       <c r="BC145" t="inlineStr"/>
+      <c r="BD145" t="inlineStr"/>
+      <c r="BE145" t="inlineStr"/>
+      <c r="BF145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -18198,7 +18599,7 @@
           <t>2030-12-23</t>
         </is>
       </c>
-      <c r="X146" t="b">
+      <c r="X146" t="n">
         <v>0</v>
       </c>
       <c r="Y146" t="inlineStr">
@@ -18242,6 +18643,113 @@
       <c r="BA146" t="inlineStr"/>
       <c r="BB146" t="inlineStr"/>
       <c r="BC146" t="inlineStr"/>
+      <c r="BD146" t="inlineStr"/>
+      <c r="BE146" t="inlineStr"/>
+      <c r="BF146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Southern California Edison Eisenhower-Thornhill ACCC reconductoring</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>EISENHOWER</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>THORNHILL</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Southern California Edison (SCE)</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Line Reconductoring</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Completed case study</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>SCE reconductored the Eisenhower-Thornhill line near Palm Springs Airport to address load growth and thermal sag limitations while retaining existing structures.</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>CAISO</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr"/>
+      <c r="P147" t="inlineStr"/>
+      <c r="Q147" t="inlineStr"/>
+      <c r="R147" t="inlineStr"/>
+      <c r="S147" t="inlineStr"/>
+      <c r="T147" t="inlineStr"/>
+      <c r="U147" t="inlineStr"/>
+      <c r="V147" t="inlineStr"/>
+      <c r="W147" t="inlineStr"/>
+      <c r="X147" t="inlineStr"/>
+      <c r="Y147" t="inlineStr"/>
+      <c r="Z147" t="inlineStr"/>
+      <c r="AA147" t="inlineStr"/>
+      <c r="AB147" t="inlineStr"/>
+      <c r="AC147" t="inlineStr"/>
+      <c r="AD147" t="inlineStr"/>
+      <c r="AE147" t="inlineStr"/>
+      <c r="AF147" t="inlineStr"/>
+      <c r="AG147" t="inlineStr"/>
+      <c r="AH147" t="inlineStr"/>
+      <c r="AI147" t="inlineStr"/>
+      <c r="AJ147" t="inlineStr"/>
+      <c r="AK147" t="inlineStr"/>
+      <c r="AL147" t="inlineStr"/>
+      <c r="AM147" t="inlineStr"/>
+      <c r="AN147" t="inlineStr"/>
+      <c r="AO147" t="inlineStr"/>
+      <c r="AP147" t="inlineStr"/>
+      <c r="AQ147" t="inlineStr"/>
+      <c r="AR147" t="inlineStr"/>
+      <c r="AS147" t="inlineStr"/>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AU147" t="inlineStr"/>
+      <c r="AV147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr"/>
+      <c r="AX147" t="inlineStr"/>
+      <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr"/>
+      <c r="BA147" t="inlineStr"/>
+      <c r="BB147" t="inlineStr"/>
+      <c r="BC147" t="inlineStr"/>
+      <c r="BD147" t="inlineStr">
+        <is>
+          <t>ACCC</t>
+        </is>
+      </c>
+      <c r="BE147" t="inlineStr">
+        <is>
+          <t>EPRI Advanced Conductor Experience</t>
+        </is>
+      </c>
+      <c r="BF147" t="inlineStr">
+        <is>
+          <t>https://msites.epri.com/rd/research/024056/advanced-conductor-experience/southern-california-edison-accc</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -19565,7 +20073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19629,6 +20137,21 @@
           <t>Found On DB</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Conductor Type</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>EPRI Case URL</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19678,9 +20201,12 @@
           <t>Coordinated MISO baseline transmission upgrades rebuild and reconductor the 345 kV lines connecting Cayuga, Nucor, and Wolf Creek. The program includes a $96 million Cayuga-to-Nucor rebuild and a $49 million Nucor-to-Wolf Creek rebuild targeted for completion by June 2029.</t>
         </is>
       </c>
-      <c r="L2" t="b">
+      <c r="L2" t="n">
         <v>1</v>
       </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19716,9 +20242,12 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="b">
+      <c r="L3" t="n">
         <v>1</v>
       </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -19754,9 +20283,12 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="b">
+      <c r="L4" t="n">
         <v>0</v>
       </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -19792,9 +20324,12 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="b">
+      <c r="L5" t="n">
         <v>1</v>
       </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -19830,9 +20365,12 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="b">
+      <c r="L6" t="n">
         <v>1</v>
       </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -19868,9 +20406,12 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="b">
+      <c r="L7" t="n">
         <v>1</v>
       </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -19906,9 +20447,12 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="b">
+      <c r="L8" t="n">
         <v>1</v>
       </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19958,9 +20502,12 @@
           <t>Each individual Interconnection Customer is responsible for a proportionate percentage share of the Common Use Upgrades (CUU) estimated cost based on its proportionate impact on the constrained facilities causing the need for the CUU. J1773 is seeking interconnection service for 300 MW and J1781 is seeking interconnection service for 300 MW. Network upgrades will consist of Hill Valley – Eden 138kV (X-127) reconductor project and Eden – Highland 138 kV (X-147) rebuild project. Source record: Source: MISO MTEP; Source ID: 50518; Planning Region: West; State(s): WI; Project Type: GIP; Other Type: G-T Interconnection; Approved: 2025; Cost: 7623089; Expected ISD: 2027-10-10 00:00:00; Status: Proposed.</t>
         </is>
       </c>
-      <c r="L9" t="b">
+      <c r="L9" t="n">
         <v>1</v>
       </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20010,9 +20557,12 @@
           <t>Each individual Interconnection Customer is responsible for a proportionate percentage share of the Common Use Upgrades (CUU) estimated cost based on its proportionate impact on the constrained facilities causing the need for the CUU. J1773 is seeking interconnection service for 300 MW and J1781 is seeking interconnection service for 300 MW. Network upgrades will consist of Hill Valley – Eden 138kV (X-127) reconductor project and Eden – Highland 138 kV (X-147) rebuild project. Source record: Source: MISO MTEP; Source ID: 50518; Planning Region: West; State(s): WI; Project Type: GIP; Other Type: G-T Interconnection; Approved: 2025; Cost: 7623089; Expected ISD: 2027-10-10 00:00:00; Status: Proposed.</t>
         </is>
       </c>
-      <c r="L10" t="b">
+      <c r="L10" t="n">
         <v>1</v>
       </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -20062,9 +20612,12 @@
           <t>Reconductor Grand Tower-Campbell Hill 138 kV Line to 2000 A summer emergency capability Source record: Source: MISO MTEP; Source ID: 9740; Planning Region: Central; State(s): IL; Project Type: Other; Other Type: Age and Condition; Approved: 2025; Cost: 34900000; Expected ISD: 2029-12-01 00:00:00; Status: Proposed.</t>
         </is>
       </c>
-      <c r="L11" t="b">
+      <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -20114,9 +20667,12 @@
           <t>Rebuild and reconductor the line to increase line rating. Source record: Source: MISO MTEP; Source ID: 50195; Planning Region: West; State(s): IA; Project Type: GIP; Cost: 7500000; Expected ISD: 2027-12-01 00:00:00; Status: -.</t>
         </is>
       </c>
-      <c r="L12" t="b">
+      <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -20166,9 +20722,12 @@
           <t>Rebuild and reconductor the line to increase line rating. Source record: Source: MISO MTEP; Source ID: 50332; Planning Region: West; State(s): IA; Project Type: Other; Other Type: Local Reliability; Cost: 2200000; Expected ISD: 2027-06-01 00:00:00; Status: -.</t>
         </is>
       </c>
-      <c r="L13" t="b">
+      <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -20218,9 +20777,12 @@
           <t>Crane South Substation: expand 138kV bus into (4) CB Ring; Install 100MVA 138/69kV Transformer Bank 2; Add (2) 69kV breakers to the existing ring; construct new 69kV line to Crane Naval Base NW; reconductor 69193 line from Crane South to Crane Naval Base Source record: Source: MISO MTEP; Source ID: 50349; Planning Region: Central; State(s): IN; Project Type: Other; Other Type: Load Growth; Approved: 2025; Cost: 28966000; Expected ISD: 2027-12-07 00:00:00; Status: Proposed.</t>
         </is>
       </c>
-      <c r="L14" t="b">
+      <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -20270,9 +20832,12 @@
           <t>Line rebuild on existing ROW Source record: Source: MISO MTEP; Source ID: 50673; Planning Region: West; State(s): WI; Project Type: -; Other Type: Reliability; Approved: 2024; Cost: 17296600; Expected ISD: 2027-06-30 00:00:00; Status: Proposed.</t>
         </is>
       </c>
-      <c r="L15" t="b">
+      <c r="L15" t="n">
         <v>1</v>
       </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -20322,9 +20887,12 @@
           <t>- Source record: Source: MISO MTEP; Source ID: 25160; State(s): -; Project Type: -; Other Type: G-T Interconnection; Approved: 2023; Cost: 22432466; Expected ISD: 2028-12-01 00:00:00; Status: Planned.</t>
         </is>
       </c>
-      <c r="L16" t="b">
+      <c r="L16" t="n">
         <v>1</v>
       </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -20374,9 +20942,12 @@
           <t>- Source record: Source: MISO MTEP; Source ID: 24838; State(s): -; Project Type: -; Other Type: Reliability; Approved: 2024; Cost: 2600000; Expected ISD: 2026-06-01 00:00:00; Status: Planned.</t>
         </is>
       </c>
-      <c r="L17" t="b">
+      <c r="L17" t="n">
         <v>1</v>
       </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -20426,9 +20997,12 @@
           <t>Line reconductor Source record: Source: MISO MTEP; Source ID: 50824; Planning Region: West; State(s): WI; Project Type: Line Upgrade; Approved: 2025; Cost: 1625089; Expected ISD: 2027-10-10 00:00:00; Status: Proposed.</t>
         </is>
       </c>
-      <c r="L18" t="b">
+      <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -20478,9 +21052,12 @@
           <t>Line reconductor Source record: Source: MISO MTEP; Source ID: 50825; Planning Region: West; State(s): WI; Project Type: Line Upgrade; Approved: 2025; Cost: 5998000; Expected ISD: 2027-10-10 00:00:00; Status: Proposed.</t>
         </is>
       </c>
-      <c r="L19" t="b">
+      <c r="L19" t="n">
         <v>1</v>
       </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -20530,8 +21107,137 @@
           <t>Line reconductor Source record: Source: MISO MTEP; Source ID: 50213; Planning Region: West; State(s): IA; Project Type: Line Upgrade; Approved: 2025; Cost: 6417500; Expected ISD: 2028-12-31 00:00:00; Status: Proposed.</t>
         </is>
       </c>
-      <c r="L20" t="b">
+      <c r="L20" t="n">
         <v>1</v>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Entergy Ninemile-Napoleon 230 kV ACCR reconductoring</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>NINEMILE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NAPOLEON</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Line Reconductoring</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>230</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>MISO</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Entergy New Orleans, LLC</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Completed case study</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Entergy upgraded the Ninemile to Napoleon 230 kV line feeding the warehouse and central business district of New Orleans.</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>ACCR</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>EPRI Advanced Conductor Experience</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>https://msites.epri.com/rd/research/024056/advanced-conductor-experience/entergy-accr</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Entergy Ninemile-Derbigny 230 kV ACCR reconductoring</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NINEMILE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>DERBIGNY</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Line Reconductoring</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>230</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>MISO</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Entergy New Orleans, LLC</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Completed case study</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Entergy upgraded the Ninemile to Derbigny 230 kV line serving the New Orleans Superdome.</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>ACCR</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>EPRI Advanced Conductor Experience</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>https://msites.epri.com/rd/research/024056/advanced-conductor-experience/entergy-accr</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -20545,7 +21251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T17"/>
+  <dimension ref="A1:T16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21505,17 +22211,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Quaker-Sleight Road #13 Rebuild Line Reconductoring</t>
+          <t>Packard-Huntley 130/133 Line Reconductoring</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>QUAKER</t>
+          <t>PACKARD</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SLEIGHT ROAD</t>
+          <t>HUNTLEY</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -21535,23 +22241,23 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2033</v>
+        <v>2027</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Solution: Rebuild ~8 mi of structures and reconductor with 1590 ACSS 54/19</t>
+          <t>Solution: Reconductor ~9 mi of DCT 130/133; Change protection settings at Packard, Walck and Huntley stations</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>System Capacity</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2033-05-01T00:00:00</t>
+          <t>2027-08-01T00:00:00</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -21559,31 +22265,31 @@
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Rebuild ~8 mi of structures and reconductor with 1590 ACSS 54/19</t>
+          <t>Reconductor ~9 mi of DCT 130/133; Change protection settings at Packard, Walck and Huntley stations</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Packard-Huntley 130/133 Line Reconductoring</t>
+          <t>Reconductor Cortland- Clarks Corners Line Reconductoring</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PACKARD</t>
+          <t>CORTLAND</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>HUNTLEY</t>
+          <t>CLARKS CORNERS</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -21603,11 +22309,11 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Solution: Reconductor ~9 mi of DCT 130/133; Change protection settings at Packard, Walck and Huntley stations</t>
+          <t>Solution: Reconductor ~0.2 mi of conductor to match the rest of the line</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -21619,7 +22325,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2027-08-01T00:00:00</t>
+          <t>2028-03-01T00:00:00</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -21627,31 +22333,31 @@
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Reconductor ~9 mi of DCT 130/133; Change protection settings at Packard, Walck and Huntley stations</t>
+          <t>Reconductor ~0.2 mi of conductor to match the rest of the line</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>0.2</v>
       </c>
       <c r="T13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Reconductor Cortland- Clarks Corners Line Reconductoring</t>
+          <t>Elbridge - Geres Lock Capacity Line Reconductoring</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CORTLAND</t>
+          <t>ELBRIDGE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLARKS CORNERS</t>
+          <t>GERES LOCK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -21667,15 +22373,15 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Concept</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2028</v>
+        <v>2033</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Solution: Reconductor ~0.2 mi of conductor to match the rest of the line</t>
+          <t>Solution: Reconductor all ~8 mi of both lines (DCT); New conductor size TBD.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -21687,7 +22393,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2028-03-01T00:00:00</t>
+          <t>2033-04-01T00:00:00</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -21695,12 +22401,12 @@
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Reconductor ~0.2 mi of conductor to match the rest of the line</t>
+          <t>Reconductor all ~8 mi of both lines (DCT); New conductor size TBD.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>0.2</v>
+        <v>8</v>
       </c>
       <c r="T14" t="b">
         <v>0</v>
@@ -21709,17 +22415,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Elbridge - Geres Lock Capacity Line Reconductoring</t>
+          <t>Spier Falls - Mohican 115 kV lines 4/7/18 rebuild Line Reconductoring</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ELBRIDGE</t>
+          <t>SPIER FALLS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GERES LOCK</t>
+          <t>MOHICAN</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -21739,23 +22445,23 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Solution: Reconductor all ~8 mi of both lines (DCT); New conductor size TBD.</t>
+          <t>Solution: Rebuild/reconductor 9.44 mi of double circuit 115 kV between Spier Falls and Mohican</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>System Capacity</t>
+          <t>MVT</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2033-04-01T00:00:00</t>
+          <t>2032-01-01T00:00:00</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -21763,31 +22469,33 @@
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Reconductor all ~8 mi of both lines (DCT); New conductor size TBD.</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr"/>
+          <t>Rebuild/reconductor 9.44 mi of double circuit 115 kV between Spier Falls and Mohican</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>115</v>
+      </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>9.44</v>
       </c>
       <c r="T15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Spier Falls - Mohican 115 kV lines 4/7/18 rebuild Line Reconductoring</t>
+          <t>Lasher Rd Line 1 three span reconductor Line Reconductoring</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SPIER FALLS</t>
+          <t>LASHER ROAD</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MOHICAN</t>
+          <t>LINE 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -21811,19 +22519,19 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Solution: Rebuild/reconductor 9.44 mi of double circuit 115 kV between Spier Falls and Mohican</t>
+          <t>Solution: Reconductor the first three spans of Lasher Rd LN1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>MVT</t>
+          <t>System Capacity</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2032-01-01T00:00:00</t>
+          <t>2032-06-01T00:00:00</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -21831,82 +22539,12 @@
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Rebuild/reconductor 9.44 mi of double circuit 115 kV between Spier Falls and Mohican</t>
-        </is>
-      </c>
-      <c r="R16" t="n">
-        <v>115</v>
-      </c>
-      <c r="S16" t="n">
-        <v>9.44</v>
-      </c>
+          <t>Reconductor the first three spans of Lasher Rd LN1</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
       <c r="T16" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Lasher Rd Line 1 three span reconductor Line Reconductoring</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>LASHER ROAD</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>LINE 1</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Line Reconductoring</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>NYISO</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Concept</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>2032</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Solution: Reconductor the first three spans of Lasher Rd LN1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>System Capacity</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2032-06-01T00:00:00</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Reconductor the first three spans of Lasher Rd LN1</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="b">
         <v>0</v>
       </c>
     </row>
@@ -21921,7 +22559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N97"/>
+  <dimension ref="A1:R98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21995,6 +22633,26 @@
           <t>Found On DB</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Conductor Type</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>EPRI Case URL</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Endpoint Match Info</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22054,9 +22712,13 @@
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="b">
+      <c r="N2" t="n">
         <v>1</v>
       </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -22114,9 +22776,13 @@
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="b">
+      <c r="N3" t="n">
         <v>1</v>
       </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -22178,9 +22844,13 @@
           <t>439 - 510 MVA</t>
         </is>
       </c>
-      <c r="N4" t="b">
+      <c r="N4" t="n">
         <v>1</v>
       </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -22238,9 +22908,13 @@
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="b">
+      <c r="N5" t="n">
         <v>1</v>
       </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -22299,9 +22973,13 @@
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="b">
+      <c r="N6" t="n">
         <v>1</v>
       </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -22361,9 +23039,13 @@
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="b">
+      <c r="N7" t="n">
         <v>1</v>
       </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -22415,9 +23097,13 @@
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="b">
+      <c r="N8" t="n">
         <v>1</v>
       </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -22479,9 +23165,13 @@
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="b">
+      <c r="N9" t="n">
         <v>1</v>
       </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -22541,9 +23231,13 @@
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="b">
+      <c r="N10" t="n">
         <v>1</v>
       </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -22601,9 +23295,13 @@
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="b">
+      <c r="N11" t="n">
         <v>1</v>
       </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -22657,9 +23355,13 @@
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="b">
+      <c r="N12" t="n">
         <v>1</v>
       </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -22717,9 +23419,13 @@
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="b">
+      <c r="N13" t="n">
         <v>1</v>
       </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -22781,9 +23487,13 @@
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="b">
+      <c r="N14" t="n">
         <v>1</v>
       </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -22843,9 +23553,13 @@
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="b">
+      <c r="N15" t="n">
         <v>1</v>
       </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -22909,9 +23623,13 @@
           <t>1573 MVA</t>
         </is>
       </c>
-      <c r="N16" t="b">
+      <c r="N16" t="n">
         <v>1</v>
       </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -22973,9 +23691,13 @@
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="b">
+      <c r="N17" t="n">
         <v>1</v>
       </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -23033,9 +23755,13 @@
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="b">
+      <c r="N18" t="n">
         <v>1</v>
       </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -23093,9 +23819,13 @@
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="b">
+      <c r="N19" t="n">
         <v>1</v>
       </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -23155,9 +23885,13 @@
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="b">
+      <c r="N20" t="n">
         <v>1</v>
       </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -23217,9 +23951,13 @@
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="b">
+      <c r="N21" t="n">
         <v>1</v>
       </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -23281,9 +24019,13 @@
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="b">
+      <c r="N22" t="n">
         <v>1</v>
       </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -23347,9 +24089,13 @@
           <t>1573 MVA</t>
         </is>
       </c>
-      <c r="N23" t="b">
+      <c r="N23" t="n">
         <v>1</v>
       </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -23411,9 +24157,13 @@
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="b">
+      <c r="N24" t="n">
         <v>1</v>
       </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -23465,9 +24215,13 @@
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="b">
+      <c r="N25" t="n">
         <v>0</v>
       </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -23519,9 +24273,13 @@
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="b">
+      <c r="N26" t="n">
         <v>0</v>
       </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -23575,9 +24333,13 @@
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="b">
+      <c r="N27" t="n">
         <v>0</v>
       </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -23633,9 +24395,13 @@
           <t>1573 MVA</t>
         </is>
       </c>
-      <c r="N28" t="b">
+      <c r="N28" t="n">
         <v>0</v>
       </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -23691,9 +24457,13 @@
           <t>1573 MVA</t>
         </is>
       </c>
-      <c r="N29" t="b">
+      <c r="N29" t="n">
         <v>0</v>
       </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -23749,9 +24519,13 @@
           <t>1573 MVA</t>
         </is>
       </c>
-      <c r="N30" t="b">
+      <c r="N30" t="n">
         <v>0</v>
       </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -23803,9 +24577,13 @@
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="b">
+      <c r="N31" t="n">
         <v>0</v>
       </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -23857,9 +24635,13 @@
         </is>
       </c>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="b">
+      <c r="N32" t="n">
         <v>0</v>
       </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -23911,9 +24693,13 @@
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="b">
+      <c r="N33" t="n">
         <v>0</v>
       </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -23936,10 +24722,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E34" t="n">
+        <v>230</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -23951,10 +24735,8 @@
           <t>PPL</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
+      <c r="H34" t="n">
+        <v>0.33</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -23971,9 +24753,13 @@
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="b">
+      <c r="N34" t="n">
         <v>0</v>
       </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -24011,10 +24797,8 @@
           <t>AEP</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
+      <c r="H35" t="n">
+        <v>0.8</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -24031,9 +24815,13 @@
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="b">
+      <c r="N35" t="n">
         <v>0</v>
       </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -24056,10 +24844,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
+      <c r="E36" t="n">
+        <v>138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -24088,9 +24874,13 @@
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="b">
+      <c r="N36" t="n">
         <v>0</v>
       </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -24149,9 +24939,13 @@
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" t="b">
+      <c r="N37" t="n">
         <v>0</v>
       </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -24174,10 +24968,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
+      <c r="E38" t="n">
+        <v>138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -24189,10 +24981,8 @@
           <t>APS</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="H38" t="n">
+        <v>0.5</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -24209,9 +24999,13 @@
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="b">
+      <c r="N38" t="n">
         <v>0</v>
       </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -24234,10 +25028,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
+      <c r="E39" t="n">
+        <v>69</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -24249,10 +25041,8 @@
           <t>PSEG</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="H39" t="n">
+        <v>2</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -24273,9 +25063,13 @@
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="b">
+      <c r="N39" t="n">
         <v>0</v>
       </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -24298,10 +25092,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
+      <c r="E40" t="n">
+        <v>69</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -24329,9 +25121,13 @@
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" t="b">
+      <c r="N40" t="n">
         <v>0</v>
       </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -24354,10 +25150,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E41" t="n">
+        <v>230</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -24369,10 +25163,8 @@
           <t>Dominion</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="H41" t="n">
+        <v>3</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -24390,9 +25182,13 @@
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" t="b">
+      <c r="N41" t="n">
         <v>1</v>
       </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -24415,10 +25211,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E42" t="n">
+        <v>230</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -24446,9 +25240,13 @@
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" t="b">
+      <c r="N42" t="n">
         <v>0</v>
       </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -24471,10 +25269,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E43" t="n">
+        <v>230</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -24503,9 +25299,13 @@
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" t="b">
+      <c r="N43" t="n">
         <v>0</v>
       </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -24528,10 +25328,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E44" t="n">
+        <v>230</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -24543,10 +25341,8 @@
           <t>PPL</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
+      <c r="H44" t="n">
+        <v>24.9</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -24563,9 +25359,13 @@
         </is>
       </c>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" t="b">
+      <c r="N44" t="n">
         <v>0</v>
       </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -24588,10 +25388,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E45" t="n">
+        <v>230</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -24619,9 +25417,13 @@
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" t="b">
+      <c r="N45" t="n">
         <v>0</v>
       </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -24644,10 +25446,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E46" t="n">
+        <v>230</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -24675,9 +25475,13 @@
         </is>
       </c>
       <c r="M46" t="inlineStr"/>
-      <c r="N46" t="b">
+      <c r="N46" t="n">
         <v>0</v>
       </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -24700,10 +25504,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E47" t="n">
+        <v>230</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -24731,9 +25533,13 @@
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" t="b">
+      <c r="N47" t="n">
         <v>0</v>
       </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -24756,10 +25562,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E48" t="n">
+        <v>230</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -24787,9 +25591,13 @@
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
-      <c r="N48" t="b">
+      <c r="N48" t="n">
         <v>0</v>
       </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -24812,10 +25620,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E49" t="n">
+        <v>230</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -24843,9 +25649,13 @@
         </is>
       </c>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" t="b">
+      <c r="N49" t="n">
         <v>0</v>
       </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -24868,10 +25678,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E50" t="n">
+        <v>230</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -24899,9 +25707,13 @@
         </is>
       </c>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" t="b">
+      <c r="N50" t="n">
         <v>0</v>
       </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -24924,10 +25736,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E51" t="n">
+        <v>230</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -24955,9 +25765,13 @@
         </is>
       </c>
       <c r="M51" t="inlineStr"/>
-      <c r="N51" t="b">
+      <c r="N51" t="n">
         <v>0</v>
       </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -24995,10 +25809,8 @@
           <t>AEP</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>3.95</t>
-        </is>
+      <c r="H52" t="n">
+        <v>3.95</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -25015,9 +25827,13 @@
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
-      <c r="N52" t="b">
+      <c r="N52" t="n">
         <v>0</v>
       </c>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -25040,10 +25856,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
+      <c r="E53" t="n">
+        <v>138</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -25071,9 +25885,13 @@
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
-      <c r="N53" t="b">
+      <c r="N53" t="n">
         <v>0</v>
       </c>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -25096,10 +25914,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
+      <c r="E54" t="n">
+        <v>345</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -25111,10 +25927,8 @@
           <t>ComEd</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+      <c r="H54" t="n">
+        <v>1.5</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -25131,9 +25945,13 @@
         </is>
       </c>
       <c r="M54" t="inlineStr"/>
-      <c r="N54" t="b">
+      <c r="N54" t="n">
         <v>0</v>
       </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -25156,10 +25974,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
+      <c r="E55" t="n">
+        <v>345</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -25171,10 +25987,8 @@
           <t>AEP</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>10.2</t>
-        </is>
+      <c r="H55" t="n">
+        <v>10.2</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -25191,9 +26005,13 @@
         </is>
       </c>
       <c r="M55" t="inlineStr"/>
-      <c r="N55" t="b">
+      <c r="N55" t="n">
         <v>0</v>
       </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -25216,10 +26034,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
+      <c r="E56" t="n">
+        <v>345</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -25231,10 +26047,8 @@
           <t>AEP</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
+      <c r="H56" t="n">
+        <v>4.75</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -25251,9 +26065,13 @@
         </is>
       </c>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" t="b">
+      <c r="N56" t="n">
         <v>0</v>
       </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -25276,10 +26094,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E57" t="n">
+        <v>230</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -25291,10 +26107,8 @@
           <t>Dominion</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
+      <c r="H57" t="n">
+        <v>1.24</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -25311,9 +26125,13 @@
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
-      <c r="N57" t="b">
+      <c r="N57" t="n">
         <v>0</v>
       </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -25336,10 +26154,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E58" t="n">
+        <v>230</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -25367,9 +26183,13 @@
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" t="b">
+      <c r="N58" t="n">
         <v>0</v>
       </c>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -25392,10 +26212,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E59" t="n">
+        <v>230</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -25423,9 +26241,13 @@
         </is>
       </c>
       <c r="M59" t="inlineStr"/>
-      <c r="N59" t="b">
+      <c r="N59" t="n">
         <v>0</v>
       </c>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -25448,10 +26270,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E60" t="n">
+        <v>230</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -25480,9 +26300,13 @@
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" t="b">
+      <c r="N60" t="n">
         <v>0</v>
       </c>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -25505,10 +26329,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
+      <c r="E61" t="n">
+        <v>138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -25536,9 +26358,13 @@
         </is>
       </c>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" t="b">
+      <c r="N61" t="n">
         <v>0</v>
       </c>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -25561,10 +26387,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E62" t="n">
+        <v>230</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -25576,10 +26400,8 @@
           <t>DPL</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>8.8</t>
-        </is>
+      <c r="H62" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -25596,9 +26418,13 @@
         </is>
       </c>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" t="b">
+      <c r="N62" t="n">
         <v>0</v>
       </c>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -25621,10 +26447,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E63" t="n">
+        <v>230</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -25636,10 +26460,8 @@
           <t>PENELEC</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>13.01</t>
-        </is>
+      <c r="H63" t="n">
+        <v>13.01</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -25654,9 +26476,13 @@
         </is>
       </c>
       <c r="M63" t="inlineStr"/>
-      <c r="N63" t="b">
+      <c r="N63" t="n">
         <v>0</v>
       </c>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -25679,10 +26505,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
+      <c r="E64" t="n">
+        <v>138</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -25694,10 +26518,8 @@
           <t>ATSI</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
+      <c r="H64" t="n">
+        <v>6.5</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -25714,9 +26536,13 @@
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" t="b">
+      <c r="N64" t="n">
         <v>1</v>
       </c>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -25739,10 +26565,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
+      <c r="E65" t="n">
+        <v>115</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -25754,10 +26578,8 @@
           <t>Dominion</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>10.5</t>
-        </is>
+      <c r="H65" t="n">
+        <v>10.5</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -25775,9 +26597,13 @@
         </is>
       </c>
       <c r="M65" t="inlineStr"/>
-      <c r="N65" t="b">
+      <c r="N65" t="n">
         <v>0</v>
       </c>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -25800,10 +26626,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
+      <c r="E66" t="n">
+        <v>115</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -25815,10 +26639,8 @@
           <t>ME</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>7.6</t>
-        </is>
+      <c r="H66" t="n">
+        <v>7.6</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -25835,9 +26657,13 @@
         </is>
       </c>
       <c r="M66" t="inlineStr"/>
-      <c r="N66" t="b">
+      <c r="N66" t="n">
         <v>0</v>
       </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -25860,10 +26686,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E67" t="n">
+        <v>230</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -25891,9 +26715,13 @@
         </is>
       </c>
       <c r="M67" t="inlineStr"/>
-      <c r="N67" t="b">
+      <c r="N67" t="n">
         <v>0</v>
       </c>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -25916,10 +26744,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
+      <c r="E68" t="n">
+        <v>138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -25931,10 +26757,8 @@
           <t>APS</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>27.3</t>
-        </is>
+      <c r="H68" t="n">
+        <v>27.3</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -25951,9 +26775,13 @@
         </is>
       </c>
       <c r="M68" t="inlineStr"/>
-      <c r="N68" t="b">
+      <c r="N68" t="n">
         <v>0</v>
       </c>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -25976,10 +26804,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E69" t="n">
+        <v>230</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -25991,10 +26817,8 @@
           <t>Dominion</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="H69" t="n">
+        <v>0.5</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -26011,9 +26835,13 @@
         </is>
       </c>
       <c r="M69" t="inlineStr"/>
-      <c r="N69" t="b">
+      <c r="N69" t="n">
         <v>0</v>
       </c>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -26036,10 +26864,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E70" t="n">
+        <v>230</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -26051,10 +26877,8 @@
           <t>Dominion</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="H70" t="n">
+        <v>0.5</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -26071,9 +26895,13 @@
         </is>
       </c>
       <c r="M70" t="inlineStr"/>
-      <c r="N70" t="b">
+      <c r="N70" t="n">
         <v>0</v>
       </c>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -26096,10 +26924,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E71" t="n">
+        <v>230</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -26127,9 +26953,13 @@
         </is>
       </c>
       <c r="M71" t="inlineStr"/>
-      <c r="N71" t="b">
+      <c r="N71" t="n">
         <v>0</v>
       </c>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -26152,10 +26982,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E72" t="n">
+        <v>230</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -26167,10 +26995,8 @@
           <t>Dominion</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
+      <c r="H72" t="n">
+        <v>1.47</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -26187,9 +27013,13 @@
         </is>
       </c>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" t="b">
+      <c r="N72" t="n">
         <v>0</v>
       </c>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -26212,10 +27042,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E73" t="n">
+        <v>230</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -26227,10 +27055,8 @@
           <t>Dominion</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>0.67</t>
-        </is>
+      <c r="H73" t="n">
+        <v>0.67</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -26247,9 +27073,13 @@
         </is>
       </c>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" t="b">
+      <c r="N73" t="n">
         <v>1</v>
       </c>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -26272,10 +27102,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
+      <c r="E74" t="n">
+        <v>138</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -26287,10 +27115,8 @@
           <t>APS</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>3.49</t>
-        </is>
+      <c r="H74" t="n">
+        <v>3.49</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -26307,9 +27133,13 @@
         </is>
       </c>
       <c r="M74" t="inlineStr"/>
-      <c r="N74" t="b">
+      <c r="N74" t="n">
         <v>0</v>
       </c>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -26332,10 +27162,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E75" t="n">
+        <v>230</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -26347,10 +27175,8 @@
           <t>Dominion</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>24.42</t>
-        </is>
+      <c r="H75" t="n">
+        <v>24.42</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -26367,9 +27193,13 @@
         </is>
       </c>
       <c r="M75" t="inlineStr"/>
-      <c r="N75" t="b">
+      <c r="N75" t="n">
         <v>1</v>
       </c>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -26392,10 +27222,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E76" t="n">
+        <v>230</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -26407,10 +27235,8 @@
           <t>Dominion</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
+      <c r="H76" t="n">
+        <v>1.07</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -26427,9 +27253,13 @@
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
-      <c r="N76" t="b">
+      <c r="N76" t="n">
         <v>0</v>
       </c>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -26452,10 +27282,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E77" t="n">
+        <v>230</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -26467,10 +27295,8 @@
           <t>Dominion</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>1.4</t>
-        </is>
+      <c r="H77" t="n">
+        <v>1.4</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -26487,9 +27313,13 @@
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
-      <c r="N77" t="b">
+      <c r="N77" t="n">
         <v>0</v>
       </c>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -26512,10 +27342,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E78" t="n">
+        <v>230</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -26527,10 +27355,8 @@
           <t>Dominion</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>2.9</t>
-        </is>
+      <c r="H78" t="n">
+        <v>2.9</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -26547,9 +27373,13 @@
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
-      <c r="N78" t="b">
+      <c r="N78" t="n">
         <v>1</v>
       </c>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -26572,10 +27402,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E79" t="n">
+        <v>230</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -26587,10 +27415,8 @@
           <t>Dominion</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>2.9</t>
-        </is>
+      <c r="H79" t="n">
+        <v>2.9</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -26607,9 +27433,13 @@
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
-      <c r="N79" t="b">
+      <c r="N79" t="n">
         <v>1</v>
       </c>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -26632,10 +27462,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E80" t="n">
+        <v>230</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -26647,10 +27475,8 @@
           <t>Dominion</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>7.6</t>
-        </is>
+      <c r="H80" t="n">
+        <v>7.6</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -26667,9 +27493,13 @@
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
-      <c r="N80" t="b">
+      <c r="N80" t="n">
         <v>1</v>
       </c>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -26692,10 +27522,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
+      <c r="E81" t="n">
+        <v>138</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -26723,9 +27551,13 @@
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
-      <c r="N81" t="b">
+      <c r="N81" t="n">
         <v>0</v>
       </c>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -26748,10 +27580,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
+      <c r="E82" t="n">
+        <v>138</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -26763,10 +27593,8 @@
           <t>ComEd</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="H82" t="n">
+        <v>13</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -26783,9 +27611,13 @@
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
-      <c r="N82" t="b">
+      <c r="N82" t="n">
         <v>0</v>
       </c>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -26808,10 +27640,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
+      <c r="E83" t="n">
+        <v>500</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -26823,10 +27653,8 @@
           <t>Dominion</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="H83" t="n">
+        <v>3</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -26843,9 +27671,13 @@
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
-      <c r="N83" t="b">
+      <c r="N83" t="n">
         <v>1</v>
       </c>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -26868,10 +27700,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
+      <c r="E84" t="n">
+        <v>69</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -26899,9 +27729,13 @@
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
-      <c r="N84" t="b">
+      <c r="N84" t="n">
         <v>1</v>
       </c>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -26924,10 +27758,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E85" t="n">
+        <v>230</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -26955,9 +27787,13 @@
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
-      <c r="N85" t="b">
+      <c r="N85" t="n">
         <v>0</v>
       </c>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -26980,10 +27816,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E86" t="n">
+        <v>230</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -27011,9 +27845,13 @@
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
-      <c r="N86" t="b">
+      <c r="N86" t="n">
         <v>0</v>
       </c>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -27036,10 +27874,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E87" t="n">
+        <v>230</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -27067,9 +27903,13 @@
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
-      <c r="N87" t="b">
+      <c r="N87" t="n">
         <v>0</v>
       </c>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -27092,10 +27932,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E88" t="n">
+        <v>230</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -27123,9 +27961,13 @@
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
-      <c r="N88" t="b">
+      <c r="N88" t="n">
         <v>1</v>
       </c>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -27148,10 +27990,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
+      <c r="E89" t="n">
+        <v>69</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -27179,9 +28019,13 @@
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
-      <c r="N89" t="b">
+      <c r="N89" t="n">
         <v>0</v>
       </c>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -27204,10 +28048,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E90" t="n">
+        <v>230</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -27219,10 +28061,8 @@
           <t>Dominion</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>1.61</t>
-        </is>
+      <c r="H90" t="n">
+        <v>1.61</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -27239,9 +28079,13 @@
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
-      <c r="N90" t="b">
+      <c r="N90" t="n">
         <v>0</v>
       </c>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -27264,10 +28108,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E91" t="n">
+        <v>230</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -27279,10 +28121,8 @@
           <t>Dominion</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>0.62</t>
-        </is>
+      <c r="H91" t="n">
+        <v>0.62</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -27299,9 +28139,13 @@
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
-      <c r="N91" t="b">
+      <c r="N91" t="n">
         <v>0</v>
       </c>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -27324,10 +28168,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E92" t="n">
+        <v>230</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -27339,10 +28181,8 @@
           <t>Dominion</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
+      <c r="H92" t="n">
+        <v>1.52</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -27359,9 +28199,13 @@
         </is>
       </c>
       <c r="M92" t="inlineStr"/>
-      <c r="N92" t="b">
+      <c r="N92" t="n">
         <v>0</v>
       </c>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -27384,10 +28228,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E93" t="n">
+        <v>230</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -27399,10 +28241,8 @@
           <t>Dominion</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>0.64</t>
-        </is>
+      <c r="H93" t="n">
+        <v>0.64</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -27419,9 +28259,13 @@
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
-      <c r="N93" t="b">
+      <c r="N93" t="n">
         <v>0</v>
       </c>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -27444,10 +28288,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E94" t="n">
+        <v>230</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -27459,10 +28301,8 @@
           <t>Dominion</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>2.17</t>
-        </is>
+      <c r="H94" t="n">
+        <v>2.17</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -27479,9 +28319,13 @@
         </is>
       </c>
       <c r="M94" t="inlineStr"/>
-      <c r="N94" t="b">
+      <c r="N94" t="n">
         <v>0</v>
       </c>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -27504,10 +28348,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E95" t="n">
+        <v>230</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -27519,10 +28361,8 @@
           <t>Dominion</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
+      <c r="H95" t="n">
+        <v>0.84</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -27539,9 +28379,13 @@
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
-      <c r="N95" t="b">
+      <c r="N95" t="n">
         <v>0</v>
       </c>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -27564,10 +28408,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E96" t="n">
+        <v>230</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -27579,10 +28421,8 @@
           <t>Dominion</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>3.98</t>
-        </is>
+      <c r="H96" t="n">
+        <v>3.98</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -27599,9 +28439,13 @@
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
-      <c r="N96" t="b">
+      <c r="N96" t="n">
         <v>0</v>
       </c>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -27624,10 +28468,8 @@
           <t>Line Reconductoring</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
+      <c r="E97" t="n">
+        <v>230</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -27655,8 +28497,72 @@
         </is>
       </c>
       <c r="M97" t="inlineStr"/>
-      <c r="N97" t="b">
+      <c r="N97" t="n">
         <v>1</v>
+      </c>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>American Electric Power ACCC advanced-conductor applications</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Line Reconductoring</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>PJM</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>American Electric Power (AEP)</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Completed case study portfolio</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>AEP documented advanced-conductor applications over 10 years on 138-345 kV projects, primarily increasing capacity into existing load areas where new rights of way were constrained.</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>ACCC</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>EPRI Advanced Conductor Experience</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>https://msites.epri.com/rd/research/024056/advanced-conductor-experience/american-electric-power-accc</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>EPRI page describes multiple AEP projects and does not identify one terminal pair for this portfolio record.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -27670,7 +28576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC7"/>
+  <dimension ref="A1:AH9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27817,6 +28723,31 @@
       <c r="AC1" t="inlineStr">
         <is>
           <t>Found On DB</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Conductor Type</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Endpoint Match Info</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Matched Terminals</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>EPRI Case URL</t>
         </is>
       </c>
     </row>
@@ -27871,9 +28802,14 @@
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="b">
+      <c r="AC2" t="n">
         <v>1</v>
       </c>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -27990,9 +28926,14 @@
       <c r="AB3" t="n">
         <v>3.3</v>
       </c>
-      <c r="AC3" t="b">
+      <c r="AC3" t="n">
         <v>0</v>
       </c>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -28099,9 +29040,14 @@
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="b">
+      <c r="AC4" t="n">
         <v>0</v>
       </c>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -28208,9 +29154,14 @@
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="b">
+      <c r="AC5" t="n">
         <v>0</v>
       </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -28317,9 +29268,14 @@
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="b">
+      <c r="AC6" t="n">
         <v>0</v>
       </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -28426,8 +29382,189 @@
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="b">
+      <c r="AC7" t="n">
         <v>0</v>
+      </c>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>Only one of 2 terminals was found in the database: RED BLUFF. ROADRUNNER was not matched to the SPP transmission database.</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>RED BLUFF</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>WAPA Shasta-Keswick 230 kV transmission line reconductoring with 795-T16 ACCR</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SHASTA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>KESWICK</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Line Reconductoring</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>230</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SPP</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Western Area Power Administration (WAPA)</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>In-Service</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2013-2014</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>WAPA reconductored the Shasta and Keswick substations and the associated 230 kV transmission facilities with 795-T16 ACCR conductor during 2013-2014. The work addressed N-2 overload risk: loss of both Shasta-Cottonwood 230 kV lines could overload the Shasta-Keswick 230 kV line. The ACCR conductor provides over 2,000 amps, allowing each bay to carry the full 710 MW output of the Shasta power plant. The diameter-equivalent conductor met the existing sag without increasing tension and avoided major structure replacement. ACCR was used for jack-bus and drop-down jumpers; 1590 AAC connected the high-temperature strain bus to terminals not rated for high-temperature operation.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Shasta-Keswick 230 kV ACCR reconductoring</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>WAPA ACCR project case study</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>795-T16 ACCR</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Arkansas Electric Cooperative Corporation ACCR case study</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Line Reconductoring</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SPP</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Arkansas Electric Cooperative Corporation (AECC)</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Completed case study</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>AECC completed the Thomas B. Fitzhugh Generating Station at Ozark; the EPRI case documents its ACCR advanced-conductor experience.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>ACCR</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>EPRI page does not identify a defensible transmission terminal pair.</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>EPRI Advanced Conductor Experience</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>https://msites.epri.com/rd/research/024056/advanced-conductor-experience/arkansas-electric-cooperative-corporation-accr</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -28441,7 +29578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S35"/>
+  <dimension ref="A1:X38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28540,6 +29677,31 @@
           <t>Found On DB</t>
         </is>
       </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Conductor Type</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>EPRI Case URL</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Endpoint Match Info</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -28620,9 +29782,14 @@
       <c r="R2" t="n">
         <v>1205</v>
       </c>
-      <c r="S2" t="b">
+      <c r="S2" t="n">
         <v>0</v>
       </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -28699,9 +29866,14 @@
       <c r="R3" t="n">
         <v>90784</v>
       </c>
-      <c r="S3" t="b">
+      <c r="S3" t="n">
         <v>0</v>
       </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -28782,9 +29954,14 @@
       <c r="R4" t="n">
         <v>75856</v>
       </c>
-      <c r="S4" t="b">
+      <c r="S4" t="n">
         <v>0</v>
       </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -28865,9 +30042,14 @@
       <c r="R5" t="n">
         <v>75856</v>
       </c>
-      <c r="S5" t="b">
+      <c r="S5" t="n">
         <v>0</v>
       </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -28948,9 +30130,14 @@
       <c r="R6" t="n">
         <v>71106</v>
       </c>
-      <c r="S6" t="b">
+      <c r="S6" t="n">
         <v>0</v>
       </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -29027,9 +30214,14 @@
       <c r="R7" t="n">
         <v>66077</v>
       </c>
-      <c r="S7" t="b">
+      <c r="S7" t="n">
         <v>0</v>
       </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -29106,9 +30298,14 @@
       <c r="R8" t="n">
         <v>76232</v>
       </c>
-      <c r="S8" t="b">
+      <c r="S8" t="n">
         <v>0</v>
       </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -29185,9 +30382,14 @@
       <c r="R9" t="n">
         <v>86323</v>
       </c>
-      <c r="S9" t="b">
+      <c r="S9" t="n">
         <v>0</v>
       </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -29268,9 +30470,14 @@
       <c r="R10" t="n">
         <v>61228</v>
       </c>
-      <c r="S10" t="b">
+      <c r="S10" t="n">
         <v>0</v>
       </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -29351,9 +30558,14 @@
       <c r="R11" t="n">
         <v>86882</v>
       </c>
-      <c r="S11" t="b">
+      <c r="S11" t="n">
         <v>0</v>
       </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -29434,9 +30646,14 @@
       <c r="R12" t="n">
         <v>65719</v>
       </c>
-      <c r="S12" t="b">
+      <c r="S12" t="n">
         <v>0</v>
       </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -29513,9 +30730,14 @@
       <c r="R13" t="n">
         <v>87429</v>
       </c>
-      <c r="S13" t="b">
+      <c r="S13" t="n">
         <v>0</v>
       </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -29592,9 +30814,14 @@
       <c r="R14" t="n">
         <v>86321</v>
       </c>
-      <c r="S14" t="b">
+      <c r="S14" t="n">
         <v>0</v>
       </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -29671,9 +30898,14 @@
       <c r="R15" t="n">
         <v>86331</v>
       </c>
-      <c r="S15" t="b">
+      <c r="S15" t="n">
         <v>0</v>
       </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -29750,9 +30982,14 @@
       <c r="R16" t="n">
         <v>86333</v>
       </c>
-      <c r="S16" t="b">
+      <c r="S16" t="n">
         <v>0</v>
       </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -29829,9 +31066,14 @@
       <c r="R17" t="n">
         <v>86317</v>
       </c>
-      <c r="S17" t="b">
+      <c r="S17" t="n">
         <v>0</v>
       </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -29908,9 +31150,14 @@
       <c r="R18" t="n">
         <v>86315</v>
       </c>
-      <c r="S18" t="b">
+      <c r="S18" t="n">
         <v>0</v>
       </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -29991,9 +31238,14 @@
       <c r="R19" t="n">
         <v>61224</v>
       </c>
-      <c r="S19" t="b">
+      <c r="S19" t="n">
         <v>0</v>
       </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -30070,9 +31322,14 @@
       <c r="R20" t="n">
         <v>76348</v>
       </c>
-      <c r="S20" t="b">
+      <c r="S20" t="n">
         <v>0</v>
       </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -30149,9 +31406,14 @@
       <c r="R21" t="n">
         <v>86329</v>
       </c>
-      <c r="S21" t="b">
+      <c r="S21" t="n">
         <v>1</v>
       </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -30232,9 +31494,14 @@
       <c r="R22" t="n">
         <v>66118</v>
       </c>
-      <c r="S22" t="b">
+      <c r="S22" t="n">
         <v>0</v>
       </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -30311,9 +31578,14 @@
       <c r="R23" t="n">
         <v>77146</v>
       </c>
-      <c r="S23" t="b">
+      <c r="S23" t="n">
         <v>0</v>
       </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -30390,9 +31662,14 @@
       <c r="R24" t="n">
         <v>48327</v>
       </c>
-      <c r="S24" t="b">
+      <c r="S24" t="n">
         <v>0</v>
       </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -30469,9 +31746,14 @@
       <c r="R25" t="n">
         <v>77827</v>
       </c>
-      <c r="S25" t="b">
+      <c r="S25" t="n">
         <v>0</v>
       </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -30548,9 +31830,14 @@
       <c r="R26" t="n">
         <v>66208</v>
       </c>
-      <c r="S26" t="b">
+      <c r="S26" t="n">
         <v>0</v>
       </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -30631,9 +31918,14 @@
       <c r="R27" t="n">
         <v>66366</v>
       </c>
-      <c r="S27" t="b">
+      <c r="S27" t="n">
         <v>0</v>
       </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -30714,9 +32006,14 @@
       <c r="R28" t="n">
         <v>54120</v>
       </c>
-      <c r="S28" t="b">
+      <c r="S28" t="n">
         <v>0</v>
       </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -30793,9 +32090,14 @@
       <c r="R29" t="n">
         <v>66204</v>
       </c>
-      <c r="S29" t="b">
+      <c r="S29" t="n">
         <v>0</v>
       </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -30868,9 +32170,14 @@
       <c r="R30" t="n">
         <v>60526</v>
       </c>
-      <c r="S30" t="b">
+      <c r="S30" t="n">
         <v>0</v>
       </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -30943,9 +32250,14 @@
       <c r="R31" t="n">
         <v>60504</v>
       </c>
-      <c r="S31" t="b">
+      <c r="S31" t="n">
         <v>0</v>
       </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -31018,9 +32330,14 @@
       <c r="R32" t="n">
         <v>60502</v>
       </c>
-      <c r="S32" t="b">
+      <c r="S32" t="n">
         <v>0</v>
       </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -31093,9 +32410,14 @@
       <c r="R33" t="n">
         <v>60522</v>
       </c>
-      <c r="S33" t="b">
+      <c r="S33" t="n">
         <v>0</v>
       </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -31172,9 +32494,14 @@
       <c r="R34" t="n">
         <v>66120</v>
       </c>
-      <c r="S34" t="b">
+      <c r="S34" t="n">
         <v>1</v>
       </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -31251,8 +32578,219 @@
       <c r="R35" t="n">
         <v>87594</v>
       </c>
-      <c r="S35" t="b">
+      <c r="S35" t="n">
         <v>0</v>
+      </c>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Lower Colorado River Authority 138 kV ACCR case study</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Line Reconductoring</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>138</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>ERCOT</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Completed case study</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>LCRA upgraded a dual-circuit 138 kV lattice-tower line, originally built in the late 1930s with 203.2 ACSR Brahma and previously reconductored with 795 ACSR Condor.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Lower Colorado River Authority (LCRA)</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>ACCR</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>EPRI Advanced Conductor Experience</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>https://msites.epri.com/rd/research/024056/advanced-conductor-experience/lower-colorado-river-authority-accr</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>EPRI page does not identify a defensible transmission terminal pair.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CenterPoint Energy 345 kV ACSS case study</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>New transmission line and reconductoring case study</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>345</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>ERCOT</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Completed case study</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>CenterPoint Energy of Houston used an extended-capability ACSS conductor for a 2800 MVA, 345 kV line on existing towers and partially on new right of way.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>CenterPoint Energy</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>ACSS</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>EPRI Advanced Conductor Experience</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>https://msites.epri.com/rd/research/024056/advanced-conductor-experience/centerpoint-energy-acss</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>EPRI page does not identify a defensible transmission terminal pair.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Cross Timbers 345 kV ACSS and ACCR transmission case study</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>New transmission line</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>345</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>ERCOT</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>235</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Completed case study</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Cross Timbers Transmission designed, built, and operated 235 miles of double-circuit 345 kV CREZ transmission lines, a substation, and a series-compensation station.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Cross Timbers Transmission (CTT)</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>ACSS and ACCR</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>EPRI Advanced Conductor Experience</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>https://msites.epri.com/rd/research/024056/advanced-conductor-experience/cross-timbers-acss-and-accr</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>EPRI page does not identify a defensible terminal pair for the 235-mile portfolio record.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -31266,7 +32804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:AA35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31305,6 +32843,106 @@
           <t>Found On DB</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Conductor Type</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>EPRI Case URL</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Endpoint Match Info</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Distance (mi)</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Map SUB_1 Coordinates</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Map SUB_2 Coordinates</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Planned Year</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>LSP</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Primary Driver</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Asset Owner</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Projected In-Service Date</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Total Non-PTF Project Cost</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>PPA Approval</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Needs Assessment</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Solutions</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Matched Terminals</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -31335,9 +32973,29 @@
           <t>WestConnect</t>
         </is>
       </c>
-      <c r="G2" t="b">
+      <c r="G2" t="n">
         <v>1</v>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -31368,9 +33026,29 @@
           <t>WestConnect</t>
         </is>
       </c>
-      <c r="G3" t="b">
+      <c r="G3" t="n">
         <v>1</v>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -31401,9 +33079,29 @@
           <t>WestConnect</t>
         </is>
       </c>
-      <c r="G4" t="b">
+      <c r="G4" t="n">
         <v>1</v>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -31434,9 +33132,29 @@
           <t>WestConnect</t>
         </is>
       </c>
-      <c r="G5" t="b">
+      <c r="G5" t="n">
         <v>1</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -31467,9 +33185,29 @@
           <t>WestConnect</t>
         </is>
       </c>
-      <c r="G6" t="b">
+      <c r="G6" t="n">
         <v>1</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -31500,9 +33238,29 @@
           <t>WestConnect</t>
         </is>
       </c>
-      <c r="G7" t="b">
+      <c r="G7" t="n">
         <v>1</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -31533,9 +33291,29 @@
           <t>WestConnect</t>
         </is>
       </c>
-      <c r="G8" t="b">
+      <c r="G8" t="n">
         <v>1</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -31566,9 +33344,29 @@
           <t>WestConnect</t>
         </is>
       </c>
-      <c r="G9" t="b">
+      <c r="G9" t="n">
         <v>1</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -31599,9 +33397,29 @@
           <t>WestConnect</t>
         </is>
       </c>
-      <c r="G10" t="b">
+      <c r="G10" t="n">
         <v>1</v>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -31632,9 +33450,29 @@
           <t>WestConnect</t>
         </is>
       </c>
-      <c r="G11" t="b">
+      <c r="G11" t="n">
         <v>1</v>
       </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -31665,9 +33503,29 @@
           <t>WestConnect</t>
         </is>
       </c>
-      <c r="G12" t="b">
+      <c r="G12" t="n">
         <v>1</v>
       </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -31698,9 +33556,29 @@
           <t>WestConnect</t>
         </is>
       </c>
-      <c r="G13" t="b">
+      <c r="G13" t="n">
         <v>1</v>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -31731,9 +33609,29 @@
           <t>WestConnect</t>
         </is>
       </c>
-      <c r="G14" t="b">
+      <c r="G14" t="n">
         <v>1</v>
       </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -31764,9 +33662,29 @@
           <t>WestConnect</t>
         </is>
       </c>
-      <c r="G15" t="b">
+      <c r="G15" t="n">
         <v>1</v>
       </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -31797,9 +33715,29 @@
           <t>WestConnect</t>
         </is>
       </c>
-      <c r="G16" t="b">
+      <c r="G16" t="n">
         <v>1</v>
       </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -31830,9 +33768,29 @@
           <t>WestConnect</t>
         </is>
       </c>
-      <c r="G17" t="b">
+      <c r="G17" t="n">
         <v>1</v>
       </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -31863,9 +33821,29 @@
           <t>WestConnect</t>
         </is>
       </c>
-      <c r="G18" t="b">
+      <c r="G18" t="n">
         <v>1</v>
       </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -31896,9 +33874,29 @@
           <t>WestConnect</t>
         </is>
       </c>
-      <c r="G19" t="b">
+      <c r="G19" t="n">
         <v>1</v>
       </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -31929,9 +33927,29 @@
           <t>WestConnect</t>
         </is>
       </c>
-      <c r="G20" t="b">
+      <c r="G20" t="n">
         <v>1</v>
       </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -31962,9 +33980,29 @@
           <t>WestConnect</t>
         </is>
       </c>
-      <c r="G21" t="b">
+      <c r="G21" t="n">
         <v>1</v>
       </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -31995,9 +34033,29 @@
           <t>WestConnect</t>
         </is>
       </c>
-      <c r="G22" t="b">
+      <c r="G22" t="n">
         <v>1</v>
       </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -32028,9 +34086,29 @@
           <t>WestConnect</t>
         </is>
       </c>
-      <c r="G23" t="b">
+      <c r="G23" t="n">
         <v>1</v>
       </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -32061,9 +34139,29 @@
           <t>WestConnect</t>
         </is>
       </c>
-      <c r="G24" t="b">
+      <c r="G24" t="n">
         <v>1</v>
       </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -32094,9 +34192,29 @@
           <t>WestConnect</t>
         </is>
       </c>
-      <c r="G25" t="b">
+      <c r="G25" t="n">
         <v>1</v>
       </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -32127,9 +34245,29 @@
           <t>WestConnect</t>
         </is>
       </c>
-      <c r="G26" t="b">
+      <c r="G26" t="n">
         <v>1</v>
       </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -32160,9 +34298,29 @@
           <t>WestConnect</t>
         </is>
       </c>
-      <c r="G27" t="b">
+      <c r="G27" t="n">
         <v>1</v>
       </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -32193,9 +34351,29 @@
           <t>WestConnect</t>
         </is>
       </c>
-      <c r="G28" t="b">
+      <c r="G28" t="n">
         <v>1</v>
       </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -32226,9 +34404,29 @@
           <t>WestConnect</t>
         </is>
       </c>
-      <c r="G29" t="b">
+      <c r="G29" t="n">
         <v>1</v>
       </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -32259,9 +34457,29 @@
           <t>WestConnect</t>
         </is>
       </c>
-      <c r="G30" t="b">
+      <c r="G30" t="n">
         <v>1</v>
       </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -32292,8 +34510,346 @@
           <t>WestConnect</t>
         </is>
       </c>
-      <c r="G31" t="b">
+      <c r="G31" t="n">
         <v>1</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Cheyenne Light Fuel and Power 115 kV ACCC with E3X reconductoring</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Line Reconductoring</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>115</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>WestConnect</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Cheyenne Light, Fuel and Power Transmission (Black Hills Energy)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1026-kcmil Drake ACCC with E3X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Completed case study</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>A new double-circuit 115 kV line near Cheyenne, Wyoming was reconductored after unexpected load growth; the selected ACCC option was projected to carry 1843 amps after substation upgrades.</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>EPRI Advanced Conductor Experience</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>https://msites.epri.com/rd/research/024056/advanced-conductor-experience/cheyenne-light-fuel-and-power-transmission-accc-e3x</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>EPRI page identifies the Cheyenne area but does not identify the two terminal substations.</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Nevada Power 220 kV ACCC case study</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Line Reconductoring</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>WestConnect</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Nevada Power (NV Energy)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ACCC</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Completed case study</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Nevada Power, doing business as NV Energy, identified a 220 kV transmission line for an advanced-conductor upgrade.</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>EPRI Advanced Conductor Experience</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>https://msites.epri.com/rd/research/024056/advanced-conductor-experience/nevada-power-accc</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>EPRI page does not identify a defensible transmission terminal pair.</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Arizona Public Service Cactus-Altadena 69 kV ACCS C7 line</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>CACTUS</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ALTADENA</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>New transmission line</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>69</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>WestConnect</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Arizona Public Service (APS)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ACCS C7</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Planned/new line case study</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>APS planned a new 69 kV line connecting the Cactus and Altadena substations in Scottsdale, approximately 3.2 miles along Shea Boulevard.</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>EPRI Advanced Conductor Experience</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>https://msites.epri.com/rd/research/024056/advanced-conductor-experience/arizona-public-service-accs-c7-conductor</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>-111.885158,33.583494</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>-111.838963,33.591156</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Quaker-Sleight Road #13 Rebuild Line Reconductoring</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>QUAKER</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SLEIGHT ROAD</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Line Reconductoring</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>WestConnect</t>
+        </is>
+      </c>
+      <c r="G35" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1590 ACSS 54/19</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Planned</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Solution: Rebuild ~8 mi of structures and reconductor with 1590 ACSS 54/19</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>SPP project record corrected to WestConnect by geographic endpoint match</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Only 1 of 2 terminals found in the database: QUAKER. SLEIGHT ROAD was not matched to the transmission database.</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>8</v>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="n">
+        <v>2033</v>
+      </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>MVT</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2033-05-01T00:00:00</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>Rebuild ~8 mi of structures and reconductor with 1590 ACSS 54/19</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>QUAKER</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -32307,7 +34863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32321,6 +34877,100 @@
           <t>Found On DB</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Project Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Project Type</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Conductor Type</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ISO/RTO</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>EPRI Case URL</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Endpoint Match Info</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AVISTA ACSS with E3X case study</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>AVISTA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Line Reconductoring</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ACSS with E3X</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>NorthernGrid</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Completed case study</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>EPRI Advanced Conductor Experience</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://msites.epri.com/rd/research/024056/advanced-conductor-experience/avista-acss-with-e3x</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>EPRI page does not identify a defensible transmission terminal pair.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
